--- a/src/attributions/attributions_saliency_traj_194.xlsx
+++ b/src/attributions/attributions_saliency_traj_194.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GG3"/>
+  <dimension ref="A1:GG17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -999,1140 +999,9106 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6.207008937053615e-06</v>
+        <v>0.00121934711933136</v>
       </c>
       <c r="B2" t="n">
-        <v>3.398270564503036e-05</v>
+        <v>0.09296765923500061</v>
       </c>
       <c r="C2" t="n">
-        <v>8.292468919535168e-06</v>
+        <v>0.1110221445560455</v>
       </c>
       <c r="D2" t="n">
-        <v>4.727871419163421e-05</v>
+        <v>0.1912568509578705</v>
       </c>
       <c r="E2" t="n">
-        <v>6.833236511738505e-06</v>
+        <v>0.0921529158949852</v>
       </c>
       <c r="F2" t="n">
-        <v>9.081532880372833e-06</v>
+        <v>0.05955846980214119</v>
       </c>
       <c r="G2" t="n">
-        <v>1.052007337420946e-05</v>
+        <v>0.02432411164045334</v>
       </c>
       <c r="H2" t="n">
-        <v>7.513963737437734e-06</v>
+        <v>0.0317939855158329</v>
       </c>
       <c r="I2" t="n">
-        <v>2.349533133383375e-06</v>
+        <v>0.03561165928840637</v>
       </c>
       <c r="J2" t="n">
-        <v>1.217608496517641e-05</v>
+        <v>0.01364681497216225</v>
       </c>
       <c r="K2" t="n">
-        <v>3.371280035935342e-05</v>
+        <v>0.0884375274181366</v>
       </c>
       <c r="L2" t="n">
-        <v>3.327319973323029e-06</v>
+        <v>0.08913001418113708</v>
       </c>
       <c r="M2" t="n">
-        <v>4.720859942608513e-05</v>
+        <v>0.1618753373622894</v>
       </c>
       <c r="N2" t="n">
-        <v>1.560083546792157e-06</v>
+        <v>0.1148159205913544</v>
       </c>
       <c r="O2" t="n">
-        <v>2.962619328172877e-05</v>
+        <v>0.04806238785386086</v>
       </c>
       <c r="P2" t="n">
-        <v>6.752324225089978e-06</v>
+        <v>0.0137709267437458</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.435167814634042e-05</v>
+        <v>0.06875406205654144</v>
       </c>
       <c r="R2" t="n">
-        <v>1.365060052194167e-05</v>
+        <v>0.02271530218422413</v>
       </c>
       <c r="S2" t="n">
-        <v>7.247163011925295e-06</v>
+        <v>0.01556211616843939</v>
       </c>
       <c r="T2" t="n">
-        <v>1.061386228684569e-05</v>
+        <v>0.02880382537841797</v>
       </c>
       <c r="U2" t="n">
-        <v>3.10315954266116e-06</v>
+        <v>0.008829583413898945</v>
       </c>
       <c r="V2" t="n">
-        <v>1.453660843253601e-06</v>
+        <v>0.07709075510501862</v>
       </c>
       <c r="W2" t="n">
-        <v>1.073458042810671e-05</v>
+        <v>0.0002526273019611835</v>
       </c>
       <c r="X2" t="n">
-        <v>1.160010560852243e-05</v>
+        <v>0.0687299519777298</v>
       </c>
       <c r="Y2" t="n">
-        <v>8.649842584418366e-07</v>
+        <v>0.04405324906110764</v>
       </c>
       <c r="Z2" t="n">
-        <v>8.555856766179204e-06</v>
+        <v>0.00497446907684207</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.068738806177862e-06</v>
+        <v>0.09459720551967621</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.262917794520035e-05</v>
+        <v>0.04744002223014832</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.034086380968802e-05</v>
+        <v>0.04772233963012695</v>
       </c>
       <c r="AD2" t="n">
-        <v>3.526949512888677e-06</v>
+        <v>0.04777795076370239</v>
       </c>
       <c r="AE2" t="n">
-        <v>7.558767720183823e-06</v>
+        <v>0.002204457996413112</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.350382601434831e-05</v>
+        <v>0.0225486047565937</v>
       </c>
       <c r="AG2" t="n">
-        <v>4.907379206997575e-06</v>
+        <v>0.0004224791191518307</v>
       </c>
       <c r="AH2" t="n">
-        <v>3.763723725569434e-06</v>
+        <v>0.0448601022362709</v>
       </c>
       <c r="AI2" t="n">
-        <v>3.205350367352366e-06</v>
+        <v>0.05068638548254967</v>
       </c>
       <c r="AJ2" t="n">
-        <v>8.803751370578539e-06</v>
+        <v>0.03411180526018143</v>
       </c>
       <c r="AK2" t="n">
-        <v>7.812604962964542e-06</v>
+        <v>0.02593442425131798</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.779488593456335e-05</v>
+        <v>0.06168118491768837</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.138565835390182e-06</v>
+        <v>0.01997111737728119</v>
       </c>
       <c r="AN2" t="n">
-        <v>7.738740350760054e-06</v>
+        <v>1.022126525640488e-05</v>
       </c>
       <c r="AO2" t="n">
-        <v>3.335760823119926e-07</v>
+        <v>0.1190737336874008</v>
       </c>
       <c r="AP2" t="n">
-        <v>3.238922772652586e-06</v>
+        <v>0.00385434995405376</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.84550151516305e-06</v>
+        <v>0.02069849148392677</v>
       </c>
       <c r="AR2" t="n">
-        <v>4.359987542557064e-06</v>
+        <v>0.01799350790679455</v>
       </c>
       <c r="AS2" t="n">
-        <v>3.592737812141422e-06</v>
+        <v>0.04208673536777496</v>
       </c>
       <c r="AT2" t="n">
-        <v>6.571033736690879e-06</v>
+        <v>0.01190262660384178</v>
       </c>
       <c r="AU2" t="n">
-        <v>9.240879990102258e-06</v>
+        <v>0.1226269155740738</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.307885071355486e-07</v>
+        <v>0.01543915737420321</v>
       </c>
       <c r="AW2" t="n">
-        <v>2.398257311142515e-05</v>
+        <v>0.03152932226657867</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.2307197721384e-05</v>
+        <v>0.04660500213503838</v>
       </c>
       <c r="AY2" t="n">
-        <v>8.375120160053484e-06</v>
+        <v>0.01411210652440786</v>
       </c>
       <c r="AZ2" t="n">
-        <v>8.547722245566547e-06</v>
+        <v>0.0321836918592453</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.377082753606373e-06</v>
+        <v>0.01139606442302465</v>
       </c>
       <c r="BB2" t="n">
-        <v>5.418987257144181e-06</v>
+        <v>0.06658049672842026</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.33313824335346e-06</v>
+        <v>0.028263995423913</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.531264570076019e-05</v>
+        <v>0.132581427693367</v>
       </c>
       <c r="BE2" t="n">
-        <v>5.355958819563966e-06</v>
+        <v>0.09233973920345306</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.677140971878543e-05</v>
+        <v>0.1017368882894516</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.00204669656523e-06</v>
+        <v>0.1311425417661667</v>
       </c>
       <c r="BH2" t="n">
-        <v>4.498960606724722e-06</v>
+        <v>0.01107529737055302</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.9020264971914e-06</v>
+        <v>0.01160182245075703</v>
       </c>
       <c r="BJ2" t="n">
-        <v>2.209852937085088e-06</v>
+        <v>0.03234478458762169</v>
       </c>
       <c r="BK2" t="n">
-        <v>3.102837581536733e-06</v>
+        <v>0.046259555965662</v>
       </c>
       <c r="BL2" t="n">
-        <v>1.648244688112754e-05</v>
+        <v>0.003886092454195023</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.929084464791231e-05</v>
+        <v>0.06481249630451202</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.354336518488708e-07</v>
+        <v>0.009094033390283585</v>
       </c>
       <c r="BO2" t="n">
-        <v>4.301967692299513e-06</v>
+        <v>0.08257115632295609</v>
       </c>
       <c r="BP2" t="n">
-        <v>1.745186409607413e-06</v>
+        <v>0.06490179896354675</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.351095761492616e-06</v>
+        <v>0.007722754497081041</v>
       </c>
       <c r="BR2" t="n">
-        <v>2.021333784796298e-06</v>
+        <v>0.06609475612640381</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.014344547911605e-06</v>
+        <v>0.006348496302962303</v>
       </c>
       <c r="BT2" t="n">
-        <v>4.54097335023107e-06</v>
+        <v>0.0008644657209515572</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.04846976682893e-05</v>
+        <v>0.03008869290351868</v>
       </c>
       <c r="BV2" t="n">
-        <v>1.077661090675974e-05</v>
+        <v>0.1301475614309311</v>
       </c>
       <c r="BW2" t="n">
-        <v>6.49455898837914e-07</v>
+        <v>0.01105470396578312</v>
       </c>
       <c r="BX2" t="n">
-        <v>8.867767064657528e-06</v>
+        <v>0.08591608703136444</v>
       </c>
       <c r="BY2" t="n">
-        <v>8.696705663169269e-06</v>
+        <v>0.0375298298895359</v>
       </c>
       <c r="BZ2" t="n">
-        <v>4.403959792398382e-06</v>
+        <v>0.04629074782133102</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.796567736775614e-06</v>
+        <v>0.05968368798494339</v>
       </c>
       <c r="CB2" t="n">
-        <v>2.125635546690319e-06</v>
+        <v>0.02581289038062096</v>
       </c>
       <c r="CC2" t="n">
-        <v>9.166325980913825e-06</v>
+        <v>0.09559434652328491</v>
       </c>
       <c r="CD2" t="n">
-        <v>8.622519089840353e-06</v>
+        <v>0.0007035071030259132</v>
       </c>
       <c r="CE2" t="n">
-        <v>2.826956915669143e-06</v>
+        <v>0.05455619841814041</v>
       </c>
       <c r="CF2" t="n">
-        <v>1.553236188556184e-06</v>
+        <v>0.03281706944108009</v>
       </c>
       <c r="CG2" t="n">
-        <v>1.224386960529955e-05</v>
+        <v>0.0606413446366787</v>
       </c>
       <c r="CH2" t="n">
-        <v>4.20571905124234e-06</v>
+        <v>0.02051440998911858</v>
       </c>
       <c r="CI2" t="n">
-        <v>5.499940925801639e-06</v>
+        <v>0.0009050326771102846</v>
       </c>
       <c r="CJ2" t="n">
-        <v>2.302564553247066e-06</v>
+        <v>0.02029102295637131</v>
       </c>
       <c r="CK2" t="n">
-        <v>3.428687477935455e-06</v>
+        <v>0.01467753574252129</v>
       </c>
       <c r="CL2" t="n">
-        <v>6.84134022321814e-07</v>
+        <v>0.00653665978461504</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.995180011566845e-06</v>
+        <v>0.03757551684975624</v>
       </c>
       <c r="CN2" t="n">
-        <v>7.092082796589239e-07</v>
+        <v>0.00489283911883831</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.470694542149431e-06</v>
+        <v>0.02674614451825619</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.14791309897555e-05</v>
+        <v>0.05628311261534691</v>
       </c>
       <c r="CQ2" t="n">
-        <v>4.82262566947611e-06</v>
+        <v>0.03182241693139076</v>
       </c>
       <c r="CR2" t="n">
-        <v>5.650248340316466e-07</v>
+        <v>0.02268433198332787</v>
       </c>
       <c r="CS2" t="n">
-        <v>1.777498800947797e-05</v>
+        <v>0.01797765307128429</v>
       </c>
       <c r="CT2" t="n">
-        <v>2.012522236327641e-05</v>
+        <v>0.006226630415767431</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.351135961158434e-05</v>
+        <v>0.02572336047887802</v>
       </c>
       <c r="CV2" t="n">
-        <v>9.503091860096902e-06</v>
+        <v>0.009731565602123737</v>
       </c>
       <c r="CW2" t="n">
-        <v>3.951569851778913e-06</v>
+        <v>0.05078573524951935</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.858781160990475e-06</v>
+        <v>0.02951355278491974</v>
       </c>
       <c r="CY2" t="n">
-        <v>9.687634701549541e-06</v>
+        <v>0.05548170208930969</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.731374024733668e-06</v>
+        <v>0.002843296620994806</v>
       </c>
       <c r="DA2" t="n">
-        <v>7.743964488327038e-06</v>
+        <v>0.007321122102439404</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.201139639306348e-06</v>
+        <v>0.02302715554833412</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.972093398057041e-06</v>
+        <v>0.01596506126224995</v>
       </c>
       <c r="DD2" t="n">
-        <v>7.302674021048006e-07</v>
+        <v>0.01170708518475294</v>
       </c>
       <c r="DE2" t="n">
-        <v>1.884814082586672e-06</v>
+        <v>0.02168410085141659</v>
       </c>
       <c r="DF2" t="n">
-        <v>2.625177876325324e-05</v>
+        <v>0.1459063440561295</v>
       </c>
       <c r="DG2" t="n">
-        <v>1.484590575273614e-05</v>
+        <v>0.0539490133523941</v>
       </c>
       <c r="DH2" t="n">
-        <v>7.69599591876613e-06</v>
+        <v>0.02071763202548027</v>
       </c>
       <c r="DI2" t="n">
-        <v>1.203126339532901e-05</v>
+        <v>0.002807802986353636</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.003450572374277e-05</v>
+        <v>0.01839524507522583</v>
       </c>
       <c r="DK2" t="n">
-        <v>2.43749327637488e-05</v>
+        <v>0.01660290732979774</v>
       </c>
       <c r="DL2" t="n">
-        <v>1.521226181466773e-06</v>
+        <v>0.00901908241212368</v>
       </c>
       <c r="DM2" t="n">
-        <v>9.402136129210703e-06</v>
+        <v>0.06145035475492477</v>
       </c>
       <c r="DN2" t="n">
-        <v>9.288982255384326e-06</v>
+        <v>0.01319676637649536</v>
       </c>
       <c r="DO2" t="n">
-        <v>5.841021447849926e-06</v>
+        <v>0.01185515709221363</v>
       </c>
       <c r="DP2" t="n">
-        <v>1.495819651609054e-05</v>
+        <v>0.04879162460565567</v>
       </c>
       <c r="DQ2" t="n">
-        <v>1.772860377968755e-05</v>
+        <v>0.01261672750115395</v>
       </c>
       <c r="DR2" t="n">
-        <v>2.805671783789876e-06</v>
+        <v>0.06360609829425812</v>
       </c>
       <c r="DS2" t="n">
-        <v>3.169203864672454e-06</v>
+        <v>0.09304361790418625</v>
       </c>
       <c r="DT2" t="n">
-        <v>1.827886990213301e-06</v>
+        <v>0.05083980783820152</v>
       </c>
       <c r="DU2" t="n">
-        <v>4.003598405688535e-06</v>
+        <v>0.07585025578737259</v>
       </c>
       <c r="DV2" t="n">
-        <v>4.300322871131357e-06</v>
+        <v>0.03561362624168396</v>
       </c>
       <c r="DW2" t="n">
-        <v>1.284456357097952e-05</v>
+        <v>0.03733280673623085</v>
       </c>
       <c r="DX2" t="n">
-        <v>7.351048225245904e-06</v>
+        <v>0.01436735969036818</v>
       </c>
       <c r="DY2" t="n">
-        <v>4.196844656689791e-06</v>
+        <v>0.05118214711546898</v>
       </c>
       <c r="DZ2" t="n">
-        <v>7.080815066728974e-06</v>
+        <v>0.05298948287963867</v>
       </c>
       <c r="EA2" t="n">
-        <v>4.029973297292599e-06</v>
+        <v>0.1490925997495651</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.181070183520205e-05</v>
+        <v>0.1256236732006073</v>
       </c>
       <c r="EC2" t="n">
-        <v>6.004175702400971e-06</v>
+        <v>0.01304742507636547</v>
       </c>
       <c r="ED2" t="n">
-        <v>1.179560422315262e-05</v>
+        <v>0.09261902421712875</v>
       </c>
       <c r="EE2" t="n">
-        <v>3.908749931724742e-06</v>
+        <v>0.01758407242596149</v>
       </c>
       <c r="EF2" t="n">
-        <v>3.971531441493426e-07</v>
+        <v>0.02808847278356552</v>
       </c>
       <c r="EG2" t="n">
-        <v>2.010688149312045e-06</v>
+        <v>0.03693505004048347</v>
       </c>
       <c r="EH2" t="n">
-        <v>4.006948302048841e-07</v>
+        <v>0.01513146050274372</v>
       </c>
       <c r="EI2" t="n">
-        <v>2.102521466440521e-05</v>
+        <v>0.1436076164245605</v>
       </c>
       <c r="EJ2" t="n">
-        <v>4.695149982580915e-06</v>
+        <v>0.009178704582154751</v>
       </c>
       <c r="EK2" t="n">
-        <v>4.516069566307124e-06</v>
+        <v>0.02588615939021111</v>
       </c>
       <c r="EL2" t="n">
-        <v>4.736650680570165e-07</v>
+        <v>0.007150136865675449</v>
       </c>
       <c r="EM2" t="n">
-        <v>8.942884960561059e-06</v>
+        <v>0.01103311683982611</v>
       </c>
       <c r="EN2" t="n">
-        <v>2.545800498410244e-06</v>
+        <v>0.00595566164702177</v>
       </c>
       <c r="EO2" t="n">
-        <v>1.441867243556771e-05</v>
+        <v>0.003000891767442226</v>
       </c>
       <c r="EP2" t="n">
-        <v>3.076875145779923e-07</v>
+        <v>0.05083494633436203</v>
       </c>
       <c r="EQ2" t="n">
-        <v>1.225044070451986e-05</v>
+        <v>0.02302082069218159</v>
       </c>
       <c r="ER2" t="n">
-        <v>7.561968232039362e-06</v>
+        <v>0.01570148020982742</v>
       </c>
       <c r="ES2" t="n">
-        <v>1.173310693047824e-08</v>
+        <v>0.00436879601329565</v>
       </c>
       <c r="ET2" t="n">
-        <v>1.529089786345139e-05</v>
+        <v>0.01378648541867733</v>
       </c>
       <c r="EU2" t="n">
-        <v>2.343272626603721e-06</v>
+        <v>0.003981807269155979</v>
       </c>
       <c r="EV2" t="n">
-        <v>6.037987986928783e-06</v>
+        <v>0.0007368351798504591</v>
       </c>
       <c r="EW2" t="n">
-        <v>3.806934046224342e-06</v>
+        <v>0.003462188877165318</v>
       </c>
       <c r="EX2" t="n">
-        <v>1.143427198257996e-05</v>
+        <v>0.001389793120324612</v>
       </c>
       <c r="EY2" t="n">
-        <v>3.883236331603257e-06</v>
+        <v>0.06391457468271255</v>
       </c>
       <c r="EZ2" t="n">
-        <v>1.836567435020697e-06</v>
+        <v>0.02833641320466995</v>
       </c>
       <c r="FA2" t="n">
-        <v>1.16785777208861e-05</v>
+        <v>0.04741819947957993</v>
       </c>
       <c r="FB2" t="n">
-        <v>4.86442922920105e-06</v>
+        <v>0.003537452081218362</v>
       </c>
       <c r="FC2" t="n">
-        <v>5.103800958750071e-06</v>
+        <v>0.01710676960647106</v>
       </c>
       <c r="FD2" t="n">
-        <v>1.50487721839454e-07</v>
+        <v>0.01942721381783485</v>
       </c>
       <c r="FE2" t="n">
-        <v>1.431133341611712e-06</v>
+        <v>0.007342680357396603</v>
       </c>
       <c r="FF2" t="n">
-        <v>3.576625204004813e-06</v>
+        <v>0.01316146180033684</v>
       </c>
       <c r="FG2" t="n">
-        <v>5.491689080372453e-06</v>
+        <v>0.03157669305801392</v>
       </c>
       <c r="FH2" t="n">
-        <v>1.585723657626659e-05</v>
+        <v>0.07507231831550598</v>
       </c>
       <c r="FI2" t="n">
-        <v>1.875253815342148e-06</v>
+        <v>0.0560343936085701</v>
       </c>
       <c r="FJ2" t="n">
-        <v>7.331161214096937e-06</v>
+        <v>0.03030966408550739</v>
       </c>
       <c r="FK2" t="n">
-        <v>9.215464160661213e-06</v>
+        <v>0.0334855355322361</v>
       </c>
       <c r="FL2" t="n">
-        <v>3.080177066294709e-06</v>
+        <v>0.03837309405207634</v>
       </c>
       <c r="FM2" t="n">
-        <v>5.992647857055999e-06</v>
+        <v>0.02002881094813347</v>
       </c>
       <c r="FN2" t="n">
-        <v>4.265732513886178e-06</v>
+        <v>0.1451926082372665</v>
       </c>
       <c r="FO2" t="n">
-        <v>1.085860844796116e-06</v>
+        <v>0.05864667892456055</v>
       </c>
       <c r="FP2" t="n">
-        <v>2.056591984000988e-05</v>
+        <v>0.05927931144833565</v>
       </c>
       <c r="FQ2" t="n">
-        <v>1.598801463842392e-05</v>
+        <v>0.01786676980555058</v>
       </c>
       <c r="FR2" t="n">
-        <v>2.958823188237147e-06</v>
+        <v>0.08279460668563843</v>
       </c>
       <c r="FS2" t="n">
-        <v>2.473657332302537e-06</v>
+        <v>0.1497436463832855</v>
       </c>
       <c r="FT2" t="n">
-        <v>4.418377102410886e-06</v>
+        <v>0.04446884989738464</v>
       </c>
       <c r="FU2" t="n">
-        <v>7.196914339147042e-06</v>
+        <v>0.07342246919870377</v>
       </c>
       <c r="FV2" t="n">
-        <v>3.323527198517695e-05</v>
+        <v>0.003434013575315475</v>
       </c>
       <c r="FW2" t="n">
-        <v>1.819978388084564e-05</v>
+        <v>0.05116376280784607</v>
       </c>
       <c r="FX2" t="n">
-        <v>3.21456786878116e-06</v>
+        <v>0.03578867018222809</v>
       </c>
       <c r="FY2" t="n">
-        <v>2.53384823736269e-05</v>
+        <v>0.009646025486290455</v>
       </c>
       <c r="FZ2" t="n">
-        <v>2.562426288932329e-06</v>
+        <v>0.03041741997003555</v>
       </c>
       <c r="GA2" t="n">
-        <v>2.231362304883078e-05</v>
+        <v>0.01855331659317017</v>
       </c>
       <c r="GB2" t="n">
-        <v>1.92048378266918e-06</v>
+        <v>0.02407260239124298</v>
       </c>
       <c r="GC2" t="n">
-        <v>1.578045339556411e-05</v>
+        <v>0.0357489213347435</v>
       </c>
       <c r="GD2" t="n">
-        <v>1.224633888341486e-05</v>
+        <v>0.04270926862955093</v>
       </c>
       <c r="GE2" t="n">
-        <v>1.620276816538535e-05</v>
+        <v>0.03700418770313263</v>
       </c>
       <c r="GF2" t="n">
-        <v>9.347805644210894e-06</v>
+        <v>0.002533976221457124</v>
       </c>
       <c r="GG2" t="n">
-        <v>9.318232514488045e-06</v>
+        <v>0.04107120260596275</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0</v>
+        <v>0.01537091284990311</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>0.001244229846633971</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>0.0002505525771994144</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>0.007931051775813103</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>0.003162984503433108</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>0.004612504504621029</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>0.0079226428642869</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>0.003345635021105409</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>0.003565474878996611</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>0.01777096837759018</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>0.003083521500229836</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>0.00275057228282094</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>0.002016780199483037</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>0.007488907314836979</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>0.001657120417803526</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>0.01128357276320457</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>0.004600692540407181</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>0.006951449904590845</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>0.0005471828626468778</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>0.0008261934272013605</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>0.002589813899248838</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.0008090873016044497</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>0.001163692446425557</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>0.004387828521430492</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>0.0002545539755374193</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>0.001174849690869451</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>0.0003912180254701525</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>0.001066238386556506</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>0.0001649086480028927</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>0.001520107267424464</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>0.002624634187668562</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>0.006959026213735342</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>0.006493985187262297</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>0.0007484675152227283</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>0.0009759459644556046</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>0.0006329461466521025</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>0.0008600638248026371</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>0.001381000271067023</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>0.002986641367897391</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>0.002806304255500436</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>0.000632448005490005</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>0.0002685523650143296</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>0.0007746135233901441</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>0.001921205897815526</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>0.000207216537091881</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>0.009484702721238136</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>0.0009640901116654277</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>0.001517519005574286</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>0.003223720239475369</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>0.000411796907428652</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>0.002302662236616015</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>0.005636991001665592</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>0.002897295169532299</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>0.001482429914176464</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>0.001836793730035424</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>0.001484668697230518</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>7.08076695445925e-05</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>0.00396198034286499</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>0.001967915799468756</v>
       </c>
       <c r="BH3" t="n">
-        <v>0</v>
+        <v>0.0006127636879682541</v>
       </c>
       <c r="BI3" t="n">
-        <v>0</v>
+        <v>0.0004454960580915213</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0</v>
+        <v>0.00378055009059608</v>
       </c>
       <c r="BK3" t="n">
-        <v>0</v>
+        <v>0.00300561310723424</v>
       </c>
       <c r="BL3" t="n">
-        <v>0</v>
+        <v>0.004570569843053818</v>
       </c>
       <c r="BM3" t="n">
-        <v>0</v>
+        <v>0.0003015903348568827</v>
       </c>
       <c r="BN3" t="n">
-        <v>0</v>
+        <v>0.001007886952720582</v>
       </c>
       <c r="BO3" t="n">
-        <v>0</v>
+        <v>0.002975120209157467</v>
       </c>
       <c r="BP3" t="n">
-        <v>0</v>
+        <v>0.0009816458914428949</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0</v>
+        <v>0.0007570864981971681</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>0.0008499633404426277</v>
       </c>
       <c r="BS3" t="n">
-        <v>0</v>
+        <v>0.0005165741895325482</v>
       </c>
       <c r="BT3" t="n">
-        <v>0</v>
+        <v>0.002077651210129261</v>
       </c>
       <c r="BU3" t="n">
-        <v>0</v>
+        <v>0.005215143784880638</v>
       </c>
       <c r="BV3" t="n">
-        <v>0</v>
+        <v>0.0006816999521106482</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>0.005082954186946154</v>
       </c>
       <c r="BX3" t="n">
-        <v>0</v>
+        <v>0.002626902889460325</v>
       </c>
       <c r="BY3" t="n">
-        <v>0</v>
+        <v>0.0005054431967437267</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0</v>
+        <v>0.0007893035653978586</v>
       </c>
       <c r="CA3" t="n">
-        <v>0</v>
+        <v>0.002464676275849342</v>
       </c>
       <c r="CB3" t="n">
-        <v>0</v>
+        <v>0.0008244161726906896</v>
       </c>
       <c r="CC3" t="n">
-        <v>0</v>
+        <v>0.001389181124977767</v>
       </c>
       <c r="CD3" t="n">
-        <v>0</v>
+        <v>0.004400945268571377</v>
       </c>
       <c r="CE3" t="n">
-        <v>0</v>
+        <v>0.001369198318570852</v>
       </c>
       <c r="CF3" t="n">
-        <v>0</v>
+        <v>0.0008861274109221995</v>
       </c>
       <c r="CG3" t="n">
-        <v>0</v>
+        <v>0.0024478854611516</v>
       </c>
       <c r="CH3" t="n">
-        <v>0</v>
+        <v>0.0005688284290954471</v>
       </c>
       <c r="CI3" t="n">
-        <v>0</v>
+        <v>0.000556742656044662</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0</v>
+        <v>0.002313184086233377</v>
       </c>
       <c r="CK3" t="n">
-        <v>0</v>
+        <v>0.001312292646616697</v>
       </c>
       <c r="CL3" t="n">
-        <v>0</v>
+        <v>0.0002217328292317688</v>
       </c>
       <c r="CM3" t="n">
-        <v>0</v>
+        <v>8.357572369277477e-05</v>
       </c>
       <c r="CN3" t="n">
-        <v>0</v>
+        <v>0.00444366130977869</v>
       </c>
       <c r="CO3" t="n">
-        <v>0</v>
+        <v>0.003454862395301461</v>
       </c>
       <c r="CP3" t="n">
-        <v>0</v>
+        <v>0.004102614242583513</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0</v>
+        <v>0.002547271549701691</v>
       </c>
       <c r="CR3" t="n">
-        <v>0</v>
+        <v>0.007542587351053953</v>
       </c>
       <c r="CS3" t="n">
-        <v>0</v>
+        <v>0.004388994537293911</v>
       </c>
       <c r="CT3" t="n">
-        <v>0</v>
+        <v>0.00271320971660316</v>
       </c>
       <c r="CU3" t="n">
-        <v>0</v>
+        <v>0.002104333834722638</v>
       </c>
       <c r="CV3" t="n">
-        <v>0</v>
+        <v>0.003837026422843337</v>
       </c>
       <c r="CW3" t="n">
-        <v>0</v>
+        <v>0.001425995607860386</v>
       </c>
       <c r="CX3" t="n">
-        <v>0</v>
+        <v>0.0002928033645730466</v>
       </c>
       <c r="CY3" t="n">
-        <v>0</v>
+        <v>0.002146002370864153</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0</v>
+        <v>0.001873212167993188</v>
       </c>
       <c r="DA3" t="n">
-        <v>0</v>
+        <v>0.001284432597458363</v>
       </c>
       <c r="DB3" t="n">
-        <v>0</v>
+        <v>0.0025978097692132</v>
       </c>
       <c r="DC3" t="n">
-        <v>0</v>
+        <v>0.0009054801193997264</v>
       </c>
       <c r="DD3" t="n">
-        <v>0</v>
+        <v>0.0007621662225574255</v>
       </c>
       <c r="DE3" t="n">
-        <v>0</v>
+        <v>0.001311448635533452</v>
       </c>
       <c r="DF3" t="n">
-        <v>0</v>
+        <v>0.00898462813347578</v>
       </c>
       <c r="DG3" t="n">
-        <v>0</v>
+        <v>0.001697303727269173</v>
       </c>
       <c r="DH3" t="n">
-        <v>0</v>
+        <v>0.00413700845092535</v>
       </c>
       <c r="DI3" t="n">
-        <v>0</v>
+        <v>0.006123693659901619</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0</v>
+        <v>0.004076593555510044</v>
       </c>
       <c r="DK3" t="n">
-        <v>0</v>
+        <v>0.00159605941735208</v>
       </c>
       <c r="DL3" t="n">
-        <v>0</v>
+        <v>0.003154778387397528</v>
       </c>
       <c r="DM3" t="n">
-        <v>0</v>
+        <v>0.002289765514433384</v>
       </c>
       <c r="DN3" t="n">
-        <v>0</v>
+        <v>6.196531467139721e-05</v>
       </c>
       <c r="DO3" t="n">
-        <v>0</v>
+        <v>0.001855009235441685</v>
       </c>
       <c r="DP3" t="n">
-        <v>0</v>
+        <v>0.00188557046931237</v>
       </c>
       <c r="DQ3" t="n">
-        <v>0</v>
+        <v>7.364468183368444e-05</v>
       </c>
       <c r="DR3" t="n">
-        <v>0</v>
+        <v>0.0002279220498166978</v>
       </c>
       <c r="DS3" t="n">
-        <v>0</v>
+        <v>0.001914026215672493</v>
       </c>
       <c r="DT3" t="n">
-        <v>0</v>
+        <v>0.0008880598470568657</v>
       </c>
       <c r="DU3" t="n">
-        <v>0</v>
+        <v>0.00324030895717442</v>
       </c>
       <c r="DV3" t="n">
-        <v>0</v>
+        <v>0.003483466105535626</v>
       </c>
       <c r="DW3" t="n">
-        <v>0</v>
+        <v>0.001989701762795448</v>
       </c>
       <c r="DX3" t="n">
-        <v>0</v>
+        <v>0.002266788156703115</v>
       </c>
       <c r="DY3" t="n">
-        <v>0</v>
+        <v>0.004794025793671608</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0</v>
+        <v>0.00135004660114646</v>
       </c>
       <c r="EA3" t="n">
-        <v>0</v>
+        <v>0.0001070737489499152</v>
       </c>
       <c r="EB3" t="n">
-        <v>0</v>
+        <v>0.005223360378295183</v>
       </c>
       <c r="EC3" t="n">
-        <v>0</v>
+        <v>0.004688036162406206</v>
       </c>
       <c r="ED3" t="n">
-        <v>0</v>
+        <v>0.003242644248530269</v>
       </c>
       <c r="EE3" t="n">
-        <v>0</v>
+        <v>0.001907399855554104</v>
       </c>
       <c r="EF3" t="n">
-        <v>0</v>
+        <v>0.004036490805447102</v>
       </c>
       <c r="EG3" t="n">
-        <v>0</v>
+        <v>0.002819759305566549</v>
       </c>
       <c r="EH3" t="n">
-        <v>0</v>
+        <v>0.001697281491942704</v>
       </c>
       <c r="EI3" t="n">
-        <v>0</v>
+        <v>0.006666590459644794</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0</v>
+        <v>0.0002975290699396282</v>
       </c>
       <c r="EK3" t="n">
-        <v>0</v>
+        <v>0.0008373952587135136</v>
       </c>
       <c r="EL3" t="n">
-        <v>0</v>
+        <v>0.001935573760420084</v>
       </c>
       <c r="EM3" t="n">
-        <v>0</v>
+        <v>0.0001213162613566965</v>
       </c>
       <c r="EN3" t="n">
-        <v>0</v>
+        <v>1.583911944180727e-05</v>
       </c>
       <c r="EO3" t="n">
-        <v>0</v>
+        <v>0.004404267761856318</v>
       </c>
       <c r="EP3" t="n">
-        <v>0</v>
+        <v>0.002271887147799134</v>
       </c>
       <c r="EQ3" t="n">
-        <v>0</v>
+        <v>0.0009096402209252119</v>
       </c>
       <c r="ER3" t="n">
-        <v>0</v>
+        <v>0.001061211805790663</v>
       </c>
       <c r="ES3" t="n">
-        <v>0</v>
+        <v>0.004107476677745581</v>
       </c>
       <c r="ET3" t="n">
-        <v>0</v>
+        <v>0.00147109420504421</v>
       </c>
       <c r="EU3" t="n">
-        <v>0</v>
+        <v>0.001927900826558471</v>
       </c>
       <c r="EV3" t="n">
-        <v>0</v>
+        <v>0.002624190412461758</v>
       </c>
       <c r="EW3" t="n">
-        <v>0</v>
+        <v>0.002816421212628484</v>
       </c>
       <c r="EX3" t="n">
-        <v>0</v>
+        <v>0.004970073699951172</v>
       </c>
       <c r="EY3" t="n">
-        <v>0</v>
+        <v>0.002556092338636518</v>
       </c>
       <c r="EZ3" t="n">
-        <v>0</v>
+        <v>4.447887840797193e-05</v>
       </c>
       <c r="FA3" t="n">
-        <v>0</v>
+        <v>0.002622488886117935</v>
       </c>
       <c r="FB3" t="n">
-        <v>0</v>
+        <v>0.0008770325221121311</v>
       </c>
       <c r="FC3" t="n">
-        <v>0</v>
+        <v>0.0004381144826766104</v>
       </c>
       <c r="FD3" t="n">
-        <v>0</v>
+        <v>0.002875565551221371</v>
       </c>
       <c r="FE3" t="n">
-        <v>0</v>
+        <v>0.0006617966573685408</v>
       </c>
       <c r="FF3" t="n">
-        <v>0</v>
+        <v>0.0004463309014681727</v>
       </c>
       <c r="FG3" t="n">
-        <v>0</v>
+        <v>0.006540442816913128</v>
       </c>
       <c r="FH3" t="n">
-        <v>0</v>
+        <v>0.001633643638342619</v>
       </c>
       <c r="FI3" t="n">
-        <v>0</v>
+        <v>0.003420914523303509</v>
       </c>
       <c r="FJ3" t="n">
-        <v>0</v>
+        <v>0.001549114007502794</v>
       </c>
       <c r="FK3" t="n">
-        <v>0</v>
+        <v>0.0004821045440621674</v>
       </c>
       <c r="FL3" t="n">
-        <v>0</v>
+        <v>0.002074012532830238</v>
       </c>
       <c r="FM3" t="n">
-        <v>0</v>
+        <v>0.001815579133108258</v>
       </c>
       <c r="FN3" t="n">
-        <v>0</v>
+        <v>0.000947421183809638</v>
       </c>
       <c r="FO3" t="n">
-        <v>0</v>
+        <v>0.001717744278721511</v>
       </c>
       <c r="FP3" t="n">
-        <v>0</v>
+        <v>0.006181195378303528</v>
       </c>
       <c r="FQ3" t="n">
-        <v>0</v>
+        <v>0.0002340739010833204</v>
       </c>
       <c r="FR3" t="n">
-        <v>0</v>
+        <v>0.006250974722206593</v>
       </c>
       <c r="FS3" t="n">
-        <v>0</v>
+        <v>0.001630175160244107</v>
       </c>
       <c r="FT3" t="n">
-        <v>0</v>
+        <v>0.005385392345488071</v>
       </c>
       <c r="FU3" t="n">
-        <v>0</v>
+        <v>0.001726387068629265</v>
       </c>
       <c r="FV3" t="n">
-        <v>0</v>
+        <v>0.003569828113541007</v>
       </c>
       <c r="FW3" t="n">
-        <v>0</v>
+        <v>0.0006158486357890069</v>
       </c>
       <c r="FX3" t="n">
-        <v>0</v>
+        <v>0.005063766613602638</v>
       </c>
       <c r="FY3" t="n">
-        <v>0</v>
+        <v>0.003575206035748124</v>
       </c>
       <c r="FZ3" t="n">
-        <v>0</v>
+        <v>5.318664261722006e-05</v>
       </c>
       <c r="GA3" t="n">
-        <v>0</v>
+        <v>0.0007533638272434473</v>
       </c>
       <c r="GB3" t="n">
-        <v>0</v>
+        <v>0.0009572093258611858</v>
       </c>
       <c r="GC3" t="n">
-        <v>0</v>
+        <v>0.0029381038621068</v>
       </c>
       <c r="GD3" t="n">
-        <v>0</v>
+        <v>0.007172045297920704</v>
       </c>
       <c r="GE3" t="n">
-        <v>0</v>
+        <v>0.004289374686777592</v>
       </c>
       <c r="GF3" t="n">
-        <v>0</v>
+        <v>0.0002672908885870129</v>
       </c>
       <c r="GG3" t="n">
-        <v>0</v>
+        <v>0.003382439725100994</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>0.2399097830057144</v>
+      </c>
+      <c r="B4" t="n">
+        <v>1.013849973678589</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.03761079162359238</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.1836898475885391</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.2927322387695312</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9895703792572021</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.1690250337123871</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.157779723405838</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.09867028892040253</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.07388637959957123</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1.039882898330688</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.06164567917585373</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.1307522654533386</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.1754396855831146</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.7977789044380188</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.1176356226205826</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.1562759578227997</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.08436205238103867</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.1318510472774506</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.2129693478345871</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.3514400720596313</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.1957961618900299</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.1623892039060593</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.1232104450464249</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.4611946642398834</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.2256110310554504</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.1278435438871384</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.2884005904197693</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.1974932998418808</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.08210349082946777</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.584425687789917</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.05340040102601051</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.2839564383029938</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.2065864056348801</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.3234385251998901</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.2309797555208206</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.05632561445236206</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.0975092425942421</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0.0167900025844574</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0.1256619691848755</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0.1454288065433502</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0.2058137804269791</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0.3022844195365906</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0.1407855749130249</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>0.05958401411771774</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0.06344048678874969</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0.5153886675834656</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0.215164989233017</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0.1331683993339539</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0.5208607912063599</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>0.5401260256767273</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0.2140494883060455</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0.09727467596530914</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>0.1563924551010132</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>0.1423075646162033</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>0.6358727812767029</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>0.1050949469208717</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>0.3762604892253876</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>0.480891227722168</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>0.3263684511184692</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>0.04744116961956024</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>0.244661808013916</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>0.1051215752959251</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>0.09439675509929657</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>0.07095527648925781</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>0.05201742053031921</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>0.001979410648345947</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>0.07563988119363785</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>0.1871307939291</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>0.06482656300067902</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>0.06572806835174561</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>0.1156130358576775</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>0.05694875121116638</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>0.2210309207439423</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>0.2619659304618835</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>0.1224787458777428</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>0.1506724059581757</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>0.4202522039413452</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>0.5047359466552734</v>
+      </c>
+      <c r="CB4" t="n">
+        <v>0.04084669053554535</v>
+      </c>
+      <c r="CC4" t="n">
+        <v>0.0182475745677948</v>
+      </c>
+      <c r="CD4" t="n">
+        <v>0.05417748168110847</v>
+      </c>
+      <c r="CE4" t="n">
+        <v>0.2802380621433258</v>
+      </c>
+      <c r="CF4" t="n">
+        <v>0.04677186906337738</v>
+      </c>
+      <c r="CG4" t="n">
+        <v>0.09333262592554092</v>
+      </c>
+      <c r="CH4" t="n">
+        <v>0.07426296174526215</v>
+      </c>
+      <c r="CI4" t="n">
+        <v>0.2094000726938248</v>
+      </c>
+      <c r="CJ4" t="n">
+        <v>0.02316963858902454</v>
+      </c>
+      <c r="CK4" t="n">
+        <v>0.03496584296226501</v>
+      </c>
+      <c r="CL4" t="n">
+        <v>0.01578664593398571</v>
+      </c>
+      <c r="CM4" t="n">
+        <v>0.3132940530776978</v>
+      </c>
+      <c r="CN4" t="n">
+        <v>0.5436065793037415</v>
+      </c>
+      <c r="CO4" t="n">
+        <v>0.3877679705619812</v>
+      </c>
+      <c r="CP4" t="n">
+        <v>0.2517918348312378</v>
+      </c>
+      <c r="CQ4" t="n">
+        <v>0.03604229912161827</v>
+      </c>
+      <c r="CR4" t="n">
+        <v>0.222325786948204</v>
+      </c>
+      <c r="CS4" t="n">
+        <v>0.006315246690064669</v>
+      </c>
+      <c r="CT4" t="n">
+        <v>0.1713114082813263</v>
+      </c>
+      <c r="CU4" t="n">
+        <v>0.2202626615762711</v>
+      </c>
+      <c r="CV4" t="n">
+        <v>0.03927475586533546</v>
+      </c>
+      <c r="CW4" t="n">
+        <v>0.260709285736084</v>
+      </c>
+      <c r="CX4" t="n">
+        <v>0.0116922315210104</v>
+      </c>
+      <c r="CY4" t="n">
+        <v>0.05070685595273972</v>
+      </c>
+      <c r="CZ4" t="n">
+        <v>0.05062972754240036</v>
+      </c>
+      <c r="DA4" t="n">
+        <v>0.1846622675657272</v>
+      </c>
+      <c r="DB4" t="n">
+        <v>0.03161366656422615</v>
+      </c>
+      <c r="DC4" t="n">
+        <v>0.00563731649890542</v>
+      </c>
+      <c r="DD4" t="n">
+        <v>0.01519102789461613</v>
+      </c>
+      <c r="DE4" t="n">
+        <v>0.41147780418396</v>
+      </c>
+      <c r="DF4" t="n">
+        <v>0.2085175663232803</v>
+      </c>
+      <c r="DG4" t="n">
+        <v>0.3211541175842285</v>
+      </c>
+      <c r="DH4" t="n">
+        <v>0.1344718039035797</v>
+      </c>
+      <c r="DI4" t="n">
+        <v>0.2051892429590225</v>
+      </c>
+      <c r="DJ4" t="n">
+        <v>0.7192248702049255</v>
+      </c>
+      <c r="DK4" t="n">
+        <v>0.1847102046012878</v>
+      </c>
+      <c r="DL4" t="n">
+        <v>0.2119549661874771</v>
+      </c>
+      <c r="DM4" t="n">
+        <v>0.2283026278018951</v>
+      </c>
+      <c r="DN4" t="n">
+        <v>0.03543742746114731</v>
+      </c>
+      <c r="DO4" t="n">
+        <v>0.2246249318122864</v>
+      </c>
+      <c r="DP4" t="n">
+        <v>0.1286417245864868</v>
+      </c>
+      <c r="DQ4" t="n">
+        <v>0.3082333207130432</v>
+      </c>
+      <c r="DR4" t="n">
+        <v>0.06908723711967468</v>
+      </c>
+      <c r="DS4" t="n">
+        <v>0.06274472177028656</v>
+      </c>
+      <c r="DT4" t="n">
+        <v>0.06065261736512184</v>
+      </c>
+      <c r="DU4" t="n">
+        <v>0.09133797883987427</v>
+      </c>
+      <c r="DV4" t="n">
+        <v>0.07223081588745117</v>
+      </c>
+      <c r="DW4" t="n">
+        <v>0.1521478742361069</v>
+      </c>
+      <c r="DX4" t="n">
+        <v>0.192652702331543</v>
+      </c>
+      <c r="DY4" t="n">
+        <v>0.002948835492134094</v>
+      </c>
+      <c r="DZ4" t="n">
+        <v>0.02574952691793442</v>
+      </c>
+      <c r="EA4" t="n">
+        <v>0.1816238760948181</v>
+      </c>
+      <c r="EB4" t="n">
+        <v>0.353652685880661</v>
+      </c>
+      <c r="EC4" t="n">
+        <v>0.03415653854608536</v>
+      </c>
+      <c r="ED4" t="n">
+        <v>0.339955598115921</v>
+      </c>
+      <c r="EE4" t="n">
+        <v>0.3351921439170837</v>
+      </c>
+      <c r="EF4" t="n">
+        <v>0.09019927680492401</v>
+      </c>
+      <c r="EG4" t="n">
+        <v>0.1083600670099258</v>
+      </c>
+      <c r="EH4" t="n">
+        <v>0.1362262368202209</v>
+      </c>
+      <c r="EI4" t="n">
+        <v>0.2322580367326736</v>
+      </c>
+      <c r="EJ4" t="n">
+        <v>0.05508147925138474</v>
+      </c>
+      <c r="EK4" t="n">
+        <v>0.2280784547328949</v>
+      </c>
+      <c r="EL4" t="n">
+        <v>0.1072989106178284</v>
+      </c>
+      <c r="EM4" t="n">
+        <v>0.09411206096410751</v>
+      </c>
+      <c r="EN4" t="n">
+        <v>0.05548331514000893</v>
+      </c>
+      <c r="EO4" t="n">
+        <v>0.07875146716833115</v>
+      </c>
+      <c r="EP4" t="n">
+        <v>0.1729950159788132</v>
+      </c>
+      <c r="EQ4" t="n">
+        <v>0.2336075156927109</v>
+      </c>
+      <c r="ER4" t="n">
+        <v>0.2104649394750595</v>
+      </c>
+      <c r="ES4" t="n">
+        <v>0.3402835726737976</v>
+      </c>
+      <c r="ET4" t="n">
+        <v>0.2830723226070404</v>
+      </c>
+      <c r="EU4" t="n">
+        <v>0.04641042649745941</v>
+      </c>
+      <c r="EV4" t="n">
+        <v>0.1027007400989532</v>
+      </c>
+      <c r="EW4" t="n">
+        <v>0.03707390278577805</v>
+      </c>
+      <c r="EX4" t="n">
+        <v>0.05157460272312164</v>
+      </c>
+      <c r="EY4" t="n">
+        <v>0.2380893528461456</v>
+      </c>
+      <c r="EZ4" t="n">
+        <v>0.01871387660503387</v>
+      </c>
+      <c r="FA4" t="n">
+        <v>0.03355413675308228</v>
+      </c>
+      <c r="FB4" t="n">
+        <v>0.133186548948288</v>
+      </c>
+      <c r="FC4" t="n">
+        <v>0.1861100643873215</v>
+      </c>
+      <c r="FD4" t="n">
+        <v>0.01030563563108444</v>
+      </c>
+      <c r="FE4" t="n">
+        <v>0.02563351206481457</v>
+      </c>
+      <c r="FF4" t="n">
+        <v>0.03056104108691216</v>
+      </c>
+      <c r="FG4" t="n">
+        <v>0.2331602424383163</v>
+      </c>
+      <c r="FH4" t="n">
+        <v>0.03016394749283791</v>
+      </c>
+      <c r="FI4" t="n">
+        <v>0.2102744579315186</v>
+      </c>
+      <c r="FJ4" t="n">
+        <v>0.03535535559058189</v>
+      </c>
+      <c r="FK4" t="n">
+        <v>0.1633219420909882</v>
+      </c>
+      <c r="FL4" t="n">
+        <v>0.3878432810306549</v>
+      </c>
+      <c r="FM4" t="n">
+        <v>0.1530358791351318</v>
+      </c>
+      <c r="FN4" t="n">
+        <v>0.1445317268371582</v>
+      </c>
+      <c r="FO4" t="n">
+        <v>0.4289631545543671</v>
+      </c>
+      <c r="FP4" t="n">
+        <v>0.4351146519184113</v>
+      </c>
+      <c r="FQ4" t="n">
+        <v>0.2350162863731384</v>
+      </c>
+      <c r="FR4" t="n">
+        <v>0.1674621552228928</v>
+      </c>
+      <c r="FS4" t="n">
+        <v>0.08358579874038696</v>
+      </c>
+      <c r="FT4" t="n">
+        <v>0.01781926490366459</v>
+      </c>
+      <c r="FU4" t="n">
+        <v>0.1091908365488052</v>
+      </c>
+      <c r="FV4" t="n">
+        <v>0.08181271702051163</v>
+      </c>
+      <c r="FW4" t="n">
+        <v>0.1037713438272476</v>
+      </c>
+      <c r="FX4" t="n">
+        <v>0.1130975261330605</v>
+      </c>
+      <c r="FY4" t="n">
+        <v>0.2935602068901062</v>
+      </c>
+      <c r="FZ4" t="n">
+        <v>0.09033163636922836</v>
+      </c>
+      <c r="GA4" t="n">
+        <v>0.07272975146770477</v>
+      </c>
+      <c r="GB4" t="n">
+        <v>0.09208226203918457</v>
+      </c>
+      <c r="GC4" t="n">
+        <v>0.4464950263500214</v>
+      </c>
+      <c r="GD4" t="n">
+        <v>0.2792279124259949</v>
+      </c>
+      <c r="GE4" t="n">
+        <v>0.1458830088376999</v>
+      </c>
+      <c r="GF4" t="n">
+        <v>0.1661376804113388</v>
+      </c>
+      <c r="GG4" t="n">
+        <v>0.317223459482193</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>0</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER5" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES5" t="n">
+        <v>0</v>
+      </c>
+      <c r="ET5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>0.02968575060367584</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.1365064680576324</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.03252001106739044</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.00282061193138361</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.01097536273300648</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.1433321833610535</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.02043364197015762</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.04322174191474915</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.01751092076301575</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.003534094430506229</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.162143349647522</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.04395407438278198</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.03954212740063667</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.06481015682220459</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.1542423069477081</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.004464489873498678</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.0001326780766248703</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.02038099244236946</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.00350492331199348</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.02759794145822525</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.02189682237803936</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.04529817774891853</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.03709165751934052</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.01790796965360641</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.003851410001516342</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.01474982593208551</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.0102877551689744</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.00562808895483613</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.02506617084145546</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.01217783987522125</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.04576687514781952</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.05322758108377457</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.02801210805773735</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.003453370183706284</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.08133172988891602</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.00170408608391881</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0.004601914435625076</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.04065064340829849</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0.01787891238927841</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0.02548237331211567</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0.01772403903305531</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0.01684181019663811</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0.009535512886941433</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0.03450479358434677</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0.02488207258284092</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0.003495043609291315</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0.1705766469240189</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0.02853532508015633</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0.01356939412653446</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0.05511416494846344</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0.09453395754098892</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0.01915445551276207</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>4.235364031046629e-05</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>0.01316860876977444</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0.01234642695635557</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>0.02053525298833847</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0.02726794593036175</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>0.001645047217607498</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>0.01132243033498526</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>0.001415372127667069</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>0.01069800741970539</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>0.02425155602395535</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>0.006099001970142126</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>0.01100324839353561</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>0.02507113292813301</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>0.004112665541470051</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>0.02015190944075584</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>0.01985873654484749</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>0.02426251024007797</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>0.05127719789743423</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>0.0005711351986974478</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>0.02577266842126846</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>0.01482042204588652</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>0.1040412336587906</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>0.01730508171021938</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>0.05098235607147217</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>0.02133786305785179</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>0.05677987635135651</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>0.0153519231826067</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>0.003778367070481181</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>0.01188309863209724</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>0.006928506307303905</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>0.04720205441117287</v>
+      </c>
+      <c r="CF6" t="n">
+        <v>0.004775163717567921</v>
+      </c>
+      <c r="CG6" t="n">
+        <v>0.01212853193283081</v>
+      </c>
+      <c r="CH6" t="n">
+        <v>0.002154430840164423</v>
+      </c>
+      <c r="CI6" t="n">
+        <v>0.0326109305024147</v>
+      </c>
+      <c r="CJ6" t="n">
+        <v>0.01268318761140108</v>
+      </c>
+      <c r="CK6" t="n">
+        <v>0.01080561615526676</v>
+      </c>
+      <c r="CL6" t="n">
+        <v>0.01013164408504963</v>
+      </c>
+      <c r="CM6" t="n">
+        <v>0.02926829643547535</v>
+      </c>
+      <c r="CN6" t="n">
+        <v>0.07387980073690414</v>
+      </c>
+      <c r="CO6" t="n">
+        <v>0.03724948316812515</v>
+      </c>
+      <c r="CP6" t="n">
+        <v>0.0409446507692337</v>
+      </c>
+      <c r="CQ6" t="n">
+        <v>0.02516608498990536</v>
+      </c>
+      <c r="CR6" t="n">
+        <v>0.003122415859252214</v>
+      </c>
+      <c r="CS6" t="n">
+        <v>0.02724909037351608</v>
+      </c>
+      <c r="CT6" t="n">
+        <v>0.004742736928164959</v>
+      </c>
+      <c r="CU6" t="n">
+        <v>0.001001189462840557</v>
+      </c>
+      <c r="CV6" t="n">
+        <v>0.002162986434996128</v>
+      </c>
+      <c r="CW6" t="n">
+        <v>0.04088830202817917</v>
+      </c>
+      <c r="CX6" t="n">
+        <v>0.007918364368379116</v>
+      </c>
+      <c r="CY6" t="n">
+        <v>0.006970414891839027</v>
+      </c>
+      <c r="CZ6" t="n">
+        <v>0.0006713159382343292</v>
+      </c>
+      <c r="DA6" t="n">
+        <v>0.03541545569896698</v>
+      </c>
+      <c r="DB6" t="n">
+        <v>0.006801032461225986</v>
+      </c>
+      <c r="DC6" t="n">
+        <v>0.008431045338511467</v>
+      </c>
+      <c r="DD6" t="n">
+        <v>0.007849960587918758</v>
+      </c>
+      <c r="DE6" t="n">
+        <v>0.0161544606089592</v>
+      </c>
+      <c r="DF6" t="n">
+        <v>0.02601867169141769</v>
+      </c>
+      <c r="DG6" t="n">
+        <v>0.01976818963885307</v>
+      </c>
+      <c r="DH6" t="n">
+        <v>0.003376955166459084</v>
+      </c>
+      <c r="DI6" t="n">
+        <v>0.01433655992150307</v>
+      </c>
+      <c r="DJ6" t="n">
+        <v>0.02485381439328194</v>
+      </c>
+      <c r="DK6" t="n">
+        <v>0.01163951493799686</v>
+      </c>
+      <c r="DL6" t="n">
+        <v>0.03706367686390877</v>
+      </c>
+      <c r="DM6" t="n">
+        <v>0.01768843829631805</v>
+      </c>
+      <c r="DN6" t="n">
+        <v>0.007379839662462473</v>
+      </c>
+      <c r="DO6" t="n">
+        <v>0.01981324702501297</v>
+      </c>
+      <c r="DP6" t="n">
+        <v>0.001646695658564568</v>
+      </c>
+      <c r="DQ6" t="n">
+        <v>0.01879826746881008</v>
+      </c>
+      <c r="DR6" t="n">
+        <v>0.01022472698241472</v>
+      </c>
+      <c r="DS6" t="n">
+        <v>0.007531879004091024</v>
+      </c>
+      <c r="DT6" t="n">
+        <v>0.0006397725082933903</v>
+      </c>
+      <c r="DU6" t="n">
+        <v>0.0125091727823019</v>
+      </c>
+      <c r="DV6" t="n">
+        <v>0.01492400001734495</v>
+      </c>
+      <c r="DW6" t="n">
+        <v>0.017807487398386</v>
+      </c>
+      <c r="DX6" t="n">
+        <v>0.01524186413735151</v>
+      </c>
+      <c r="DY6" t="n">
+        <v>0.02650105580687523</v>
+      </c>
+      <c r="DZ6" t="n">
+        <v>0.01613531075417995</v>
+      </c>
+      <c r="EA6" t="n">
+        <v>0.008318194188177586</v>
+      </c>
+      <c r="EB6" t="n">
+        <v>0.02804387360811234</v>
+      </c>
+      <c r="EC6" t="n">
+        <v>0.001453407225199044</v>
+      </c>
+      <c r="ED6" t="n">
+        <v>0.007432925049215555</v>
+      </c>
+      <c r="EE6" t="n">
+        <v>0.03596089780330658</v>
+      </c>
+      <c r="EF6" t="n">
+        <v>0.001153351273387671</v>
+      </c>
+      <c r="EG6" t="n">
+        <v>0.01016285456717014</v>
+      </c>
+      <c r="EH6" t="n">
+        <v>0.006595231126993895</v>
+      </c>
+      <c r="EI6" t="n">
+        <v>0.03245760500431061</v>
+      </c>
+      <c r="EJ6" t="n">
+        <v>0.01962577365338802</v>
+      </c>
+      <c r="EK6" t="n">
+        <v>0.01579501293599606</v>
+      </c>
+      <c r="EL6" t="n">
+        <v>0.001433414174243808</v>
+      </c>
+      <c r="EM6" t="n">
+        <v>0.003351267194375396</v>
+      </c>
+      <c r="EN6" t="n">
+        <v>0.009632113389670849</v>
+      </c>
+      <c r="EO6" t="n">
+        <v>0.004441376775503159</v>
+      </c>
+      <c r="EP6" t="n">
+        <v>0.02868261560797691</v>
+      </c>
+      <c r="EQ6" t="n">
+        <v>0.008403715677559376</v>
+      </c>
+      <c r="ER6" t="n">
+        <v>0.005959507077932358</v>
+      </c>
+      <c r="ES6" t="n">
+        <v>0.0253260899335146</v>
+      </c>
+      <c r="ET6" t="n">
+        <v>0.009015068411827087</v>
+      </c>
+      <c r="EU6" t="n">
+        <v>0.005786692723631859</v>
+      </c>
+      <c r="EV6" t="n">
+        <v>0.007668283767998219</v>
+      </c>
+      <c r="EW6" t="n">
+        <v>0.0002588448114693165</v>
+      </c>
+      <c r="EX6" t="n">
+        <v>0.004763579927384853</v>
+      </c>
+      <c r="EY6" t="n">
+        <v>0.0492536723613739</v>
+      </c>
+      <c r="EZ6" t="n">
+        <v>0.005513084586709738</v>
+      </c>
+      <c r="FA6" t="n">
+        <v>0.006470063701272011</v>
+      </c>
+      <c r="FB6" t="n">
+        <v>0.006607901304960251</v>
+      </c>
+      <c r="FC6" t="n">
+        <v>0.03081711381673813</v>
+      </c>
+      <c r="FD6" t="n">
+        <v>0.0148435365408659</v>
+      </c>
+      <c r="FE6" t="n">
+        <v>0.008988237008452415</v>
+      </c>
+      <c r="FF6" t="n">
+        <v>0.001116602565161884</v>
+      </c>
+      <c r="FG6" t="n">
+        <v>0.001257904805243015</v>
+      </c>
+      <c r="FH6" t="n">
+        <v>0.03563015535473824</v>
+      </c>
+      <c r="FI6" t="n">
+        <v>0.01970376446843147</v>
+      </c>
+      <c r="FJ6" t="n">
+        <v>0.01220694370567799</v>
+      </c>
+      <c r="FK6" t="n">
+        <v>0.006082256324589252</v>
+      </c>
+      <c r="FL6" t="n">
+        <v>0.04990570992231369</v>
+      </c>
+      <c r="FM6" t="n">
+        <v>0.0233989953994751</v>
+      </c>
+      <c r="FN6" t="n">
+        <v>0.04793491587042809</v>
+      </c>
+      <c r="FO6" t="n">
+        <v>0.04132162034511566</v>
+      </c>
+      <c r="FP6" t="n">
+        <v>0.01197062153369188</v>
+      </c>
+      <c r="FQ6" t="n">
+        <v>0.05434702336788177</v>
+      </c>
+      <c r="FR6" t="n">
+        <v>0.01987357437610626</v>
+      </c>
+      <c r="FS6" t="n">
+        <v>0.02790321782231331</v>
+      </c>
+      <c r="FT6" t="n">
+        <v>0.01189521048218012</v>
+      </c>
+      <c r="FU6" t="n">
+        <v>0.04308517277240753</v>
+      </c>
+      <c r="FV6" t="n">
+        <v>0.007033523172140121</v>
+      </c>
+      <c r="FW6" t="n">
+        <v>0.06324745714664459</v>
+      </c>
+      <c r="FX6" t="n">
+        <v>0.02834958955645561</v>
+      </c>
+      <c r="FY6" t="n">
+        <v>0.02023359388113022</v>
+      </c>
+      <c r="FZ6" t="n">
+        <v>0.007570438552647829</v>
+      </c>
+      <c r="GA6" t="n">
+        <v>0.03053929097950459</v>
+      </c>
+      <c r="GB6" t="n">
+        <v>0.004336367826908827</v>
+      </c>
+      <c r="GC6" t="n">
+        <v>0.0467514768242836</v>
+      </c>
+      <c r="GD6" t="n">
+        <v>0.03412116691470146</v>
+      </c>
+      <c r="GE6" t="n">
+        <v>0.01344279665499926</v>
+      </c>
+      <c r="GF6" t="n">
+        <v>0.0007131006568670273</v>
+      </c>
+      <c r="GG6" t="n">
+        <v>0.01598687469959259</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>0.4640321731567383</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0.6075611114501953</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.03803973272442818</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.06170940771698952</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.003699779510498047</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.5574271678924561</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.09580979496240616</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.2963702082633972</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.1070341616868973</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.4503913521766663</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.7496124505996704</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.06957469135522842</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.06825511902570724</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.2193639874458313</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.5739989280700684</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.1362124383449554</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.1357904970645905</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.2530498206615448</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.02493598684668541</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.09620718657970428</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.1111492142081261</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.2142187058925629</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.1215559989213943</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.1073741465806961</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.02743871510028839</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0.2320722937583923</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.06894969195127487</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.1209335625171661</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.1314588189125061</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.07895563542842865</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.2109548598527908</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.413089245557785</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.165967658162117</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.03491991385817528</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0.1825510859489441</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.05105357617139816</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0.1456546038389206</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.1966227889060974</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0.1431946456432343</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0.147858202457428</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0.1046202257275581</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0.03985586017370224</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0.09295488893985748</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0.1465397626161575</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0.1521234214305878</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0.3028199970722198</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0.5199538469314575</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0.0956084355711937</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0.03890932351350784</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0.2107668220996857</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>0.2722114622592926</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0.01790324412286282</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0.01759144105017185</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>0.1102058589458466</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>0.04715131223201752</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>0.072215735912323</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0.07186504453420639</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>0.07118163257837296</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>0.02222689986228943</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>0.1506680846214294</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>0.04009394720196724</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>0.0719861313700676</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>0.03296374902129173</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>0.0248575247824192</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>0.006483126431703568</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>0.002789493417367339</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>0.07088731974363327</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>0.00338860135525465</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>0.08134216070175171</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>0.259054571390152</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>0.1039145588874817</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>0.1093179881572723</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>0.1033366695046425</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>0.3597005605697632</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>0.09147296100854874</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>0.1486252546310425</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>0.08491025865077972</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>0.2833438813686371</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>0.006379906088113785</v>
+      </c>
+      <c r="CB7" t="n">
+        <v>0.09231036901473999</v>
+      </c>
+      <c r="CC7" t="n">
+        <v>0.1154096499085426</v>
+      </c>
+      <c r="CD7" t="n">
+        <v>0.07083117961883545</v>
+      </c>
+      <c r="CE7" t="n">
+        <v>0.206496387720108</v>
+      </c>
+      <c r="CF7" t="n">
+        <v>0.02681757882237434</v>
+      </c>
+      <c r="CG7" t="n">
+        <v>0.02287756279110909</v>
+      </c>
+      <c r="CH7" t="n">
+        <v>0.01638989895582199</v>
+      </c>
+      <c r="CI7" t="n">
+        <v>0.1774064302444458</v>
+      </c>
+      <c r="CJ7" t="n">
+        <v>0.1204451620578766</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>0.06387408077716827</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>0.04720157384872437</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>0.04494944214820862</v>
+      </c>
+      <c r="CN7" t="n">
+        <v>0.3219752907752991</v>
+      </c>
+      <c r="CO7" t="n">
+        <v>0.07136815041303635</v>
+      </c>
+      <c r="CP7" t="n">
+        <v>0.2281016111373901</v>
+      </c>
+      <c r="CQ7" t="n">
+        <v>0.2100198119878769</v>
+      </c>
+      <c r="CR7" t="n">
+        <v>0.2092770487070084</v>
+      </c>
+      <c r="CS7" t="n">
+        <v>0.0277307890355587</v>
+      </c>
+      <c r="CT7" t="n">
+        <v>0.01387681812047958</v>
+      </c>
+      <c r="CU7" t="n">
+        <v>0.008744086138904095</v>
+      </c>
+      <c r="CV7" t="n">
+        <v>0.04910016059875488</v>
+      </c>
+      <c r="CW7" t="n">
+        <v>0.1866407841444016</v>
+      </c>
+      <c r="CX7" t="n">
+        <v>0.03486823290586472</v>
+      </c>
+      <c r="CY7" t="n">
+        <v>0.01099207997322083</v>
+      </c>
+      <c r="CZ7" t="n">
+        <v>0.004309215117245913</v>
+      </c>
+      <c r="DA7" t="n">
+        <v>0.1698120534420013</v>
+      </c>
+      <c r="DB7" t="n">
+        <v>0.08646775782108307</v>
+      </c>
+      <c r="DC7" t="n">
+        <v>0.09810875356197357</v>
+      </c>
+      <c r="DD7" t="n">
+        <v>0.04431211948394775</v>
+      </c>
+      <c r="DE7" t="n">
+        <v>0.04877893254160881</v>
+      </c>
+      <c r="DF7" t="n">
+        <v>0.0726083368062973</v>
+      </c>
+      <c r="DG7" t="n">
+        <v>0.1266651153564453</v>
+      </c>
+      <c r="DH7" t="n">
+        <v>0.05335459113121033</v>
+      </c>
+      <c r="DI7" t="n">
+        <v>0.3236058056354523</v>
+      </c>
+      <c r="DJ7" t="n">
+        <v>0.01836397498846054</v>
+      </c>
+      <c r="DK7" t="n">
+        <v>0.002572216093540192</v>
+      </c>
+      <c r="DL7" t="n">
+        <v>0.06460390239953995</v>
+      </c>
+      <c r="DM7" t="n">
+        <v>0.06511694192886353</v>
+      </c>
+      <c r="DN7" t="n">
+        <v>0.04739860445261002</v>
+      </c>
+      <c r="DO7" t="n">
+        <v>0.1427002251148224</v>
+      </c>
+      <c r="DP7" t="n">
+        <v>0.07084184885025024</v>
+      </c>
+      <c r="DQ7" t="n">
+        <v>0.01784911379218102</v>
+      </c>
+      <c r="DR7" t="n">
+        <v>0.06555571407079697</v>
+      </c>
+      <c r="DS7" t="n">
+        <v>0.1883742213249207</v>
+      </c>
+      <c r="DT7" t="n">
+        <v>0.07172257453203201</v>
+      </c>
+      <c r="DU7" t="n">
+        <v>0.2777656614780426</v>
+      </c>
+      <c r="DV7" t="n">
+        <v>0.06377119570970535</v>
+      </c>
+      <c r="DW7" t="n">
+        <v>0.0996508002281189</v>
+      </c>
+      <c r="DX7" t="n">
+        <v>0.01947095617651939</v>
+      </c>
+      <c r="DY7" t="n">
+        <v>0.05247129872441292</v>
+      </c>
+      <c r="DZ7" t="n">
+        <v>0.1264175176620483</v>
+      </c>
+      <c r="EA7" t="n">
+        <v>0.2155789434909821</v>
+      </c>
+      <c r="EB7" t="n">
+        <v>0.2321675270795822</v>
+      </c>
+      <c r="EC7" t="n">
+        <v>0.03952407836914062</v>
+      </c>
+      <c r="ED7" t="n">
+        <v>0.04932377114892006</v>
+      </c>
+      <c r="EE7" t="n">
+        <v>0.09428549557924271</v>
+      </c>
+      <c r="EF7" t="n">
+        <v>0.07784071564674377</v>
+      </c>
+      <c r="EG7" t="n">
+        <v>0.01186197437345982</v>
+      </c>
+      <c r="EH7" t="n">
+        <v>0.09579462558031082</v>
+      </c>
+      <c r="EI7" t="n">
+        <v>0.2283911257982254</v>
+      </c>
+      <c r="EJ7" t="n">
+        <v>0.04549472406506538</v>
+      </c>
+      <c r="EK7" t="n">
+        <v>0.09718666970729828</v>
+      </c>
+      <c r="EL7" t="n">
+        <v>0.06674955785274506</v>
+      </c>
+      <c r="EM7" t="n">
+        <v>0.06245047599077225</v>
+      </c>
+      <c r="EN7" t="n">
+        <v>0.05730658769607544</v>
+      </c>
+      <c r="EO7" t="n">
+        <v>0.05274365469813347</v>
+      </c>
+      <c r="EP7" t="n">
+        <v>0.07339838147163391</v>
+      </c>
+      <c r="EQ7" t="n">
+        <v>0.04383999109268188</v>
+      </c>
+      <c r="ER7" t="n">
+        <v>0.02620762586593628</v>
+      </c>
+      <c r="ES7" t="n">
+        <v>0.03554302826523781</v>
+      </c>
+      <c r="ET7" t="n">
+        <v>0.1522192806005478</v>
+      </c>
+      <c r="EU7" t="n">
+        <v>0.02744566090404987</v>
+      </c>
+      <c r="EV7" t="n">
+        <v>0.06955453008413315</v>
+      </c>
+      <c r="EW7" t="n">
+        <v>0.1602602899074554</v>
+      </c>
+      <c r="EX7" t="n">
+        <v>0.07146568596363068</v>
+      </c>
+      <c r="EY7" t="n">
+        <v>0.2278551161289215</v>
+      </c>
+      <c r="EZ7" t="n">
+        <v>0.01606826484203339</v>
+      </c>
+      <c r="FA7" t="n">
+        <v>0.01175016164779663</v>
+      </c>
+      <c r="FB7" t="n">
+        <v>0.01650277338922024</v>
+      </c>
+      <c r="FC7" t="n">
+        <v>0.1708961725234985</v>
+      </c>
+      <c r="FD7" t="n">
+        <v>0.1140744984149933</v>
+      </c>
+      <c r="FE7" t="n">
+        <v>0.1065901145339012</v>
+      </c>
+      <c r="FF7" t="n">
+        <v>0.002252875128760934</v>
+      </c>
+      <c r="FG7" t="n">
+        <v>0.006323381327092648</v>
+      </c>
+      <c r="FH7" t="n">
+        <v>0.2698003947734833</v>
+      </c>
+      <c r="FI7" t="n">
+        <v>0.1190686747431755</v>
+      </c>
+      <c r="FJ7" t="n">
+        <v>0.03440715000033379</v>
+      </c>
+      <c r="FK7" t="n">
+        <v>0.0991799384355545</v>
+      </c>
+      <c r="FL7" t="n">
+        <v>0.2219338715076447</v>
+      </c>
+      <c r="FM7" t="n">
+        <v>0.1004406288266182</v>
+      </c>
+      <c r="FN7" t="n">
+        <v>0.4351855516433716</v>
+      </c>
+      <c r="FO7" t="n">
+        <v>0.0204339437186718</v>
+      </c>
+      <c r="FP7" t="n">
+        <v>0.1665438413619995</v>
+      </c>
+      <c r="FQ7" t="n">
+        <v>0.2036694139242172</v>
+      </c>
+      <c r="FR7" t="n">
+        <v>0.3551920652389526</v>
+      </c>
+      <c r="FS7" t="n">
+        <v>0.2955003380775452</v>
+      </c>
+      <c r="FT7" t="n">
+        <v>0.002992060035467148</v>
+      </c>
+      <c r="FU7" t="n">
+        <v>0.2860827147960663</v>
+      </c>
+      <c r="FV7" t="n">
+        <v>0.1240380555391312</v>
+      </c>
+      <c r="FW7" t="n">
+        <v>0.0130542479455471</v>
+      </c>
+      <c r="FX7" t="n">
+        <v>0.01587046682834625</v>
+      </c>
+      <c r="FY7" t="n">
+        <v>0.09442882984876633</v>
+      </c>
+      <c r="FZ7" t="n">
+        <v>0.09250977635383606</v>
+      </c>
+      <c r="GA7" t="n">
+        <v>0.07216037064790726</v>
+      </c>
+      <c r="GB7" t="n">
+        <v>0.1067329794168472</v>
+      </c>
+      <c r="GC7" t="n">
+        <v>0.1458117514848709</v>
+      </c>
+      <c r="GD7" t="n">
+        <v>0.09945820271968842</v>
+      </c>
+      <c r="GE7" t="n">
+        <v>0.007169358432292938</v>
+      </c>
+      <c r="GF7" t="n">
+        <v>0.1929120123386383</v>
+      </c>
+      <c r="GG7" t="n">
+        <v>0.2313359826803207</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>0</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER8" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES8" t="n">
+        <v>0</v>
+      </c>
+      <c r="ET8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>0.0008615009719505906</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0.002385033527389169</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1.134797639679164e-05</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.000729275809135288</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.0002483919961377978</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.000920626858714968</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.0002528559125494212</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.0006466502672992647</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.0001328740327153355</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.0004836073785554618</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.002614633878692985</v>
+      </c>
+      <c r="L9" t="n">
+        <v>3.933240077458322e-05</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.001001193071715534</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.0006824976298958063</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.001132604782469571</v>
+      </c>
+      <c r="P9" t="n">
+        <v>8.975043783721048e-06</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.0001337520952802151</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.0007015569135546684</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.0001590583415236324</v>
+      </c>
+      <c r="T9" t="n">
+        <v>9.519925515633076e-05</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.0001375245483359322</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.0003563213685993105</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.0005006865831092</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.0003621316864155233</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.0003025929909199476</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0.0004443842626642436</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>5.525553569896147e-05</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.0001579042582307011</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>6.644996756222099e-05</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.0001989693264476955</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.0008004726842045784</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.001092045335099101</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.0004270909412298352</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.0001062936935340986</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.000674080743920058</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>5.72195858694613e-06</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0.0002459287061356008</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.0004734824178740382</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0.0002644764317665249</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0.000378134980564937</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>2.342829247936606e-06</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0.0002032388583756983</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0.000412363006034866</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0.0002046658919425681</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>7.895311136962846e-05</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0.0004169294552411884</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0.001812469679862261</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0.0003099899331573397</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>5.053421773482114e-06</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0.001040172995999455</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>0.0006711734458804131</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>3.283961268607527e-05</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0.0002460023970343173</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>0.000281434622593224</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0.0002072092756861821</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>0.0004108473367523402</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0.0001947579439729452</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>0.0004893459263257682</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>0.0005273285205475986</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>8.098446414805949e-05</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>4.638252721633762e-05</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>0.0003188170376233757</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>0.0001664534793235362</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>5.244227213552222e-05</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>0.0001895138702820987</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>4.81177048641257e-05</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>2.425160346319899e-06</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>0.0004481847281567752</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>4.23064484493807e-05</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>0.0005972569924779236</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>0.0002329357812413946</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>0.0003884097095578909</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>0.0002611496020108461</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>0.001197586301714182</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>0.0001567634753882885</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>0.0001701060537016019</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>0.0002029962779488415</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>0.0007210206240415573</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>0.0003407267504371703</v>
+      </c>
+      <c r="CB9" t="n">
+        <v>7.693116640439257e-05</v>
+      </c>
+      <c r="CC9" t="n">
+        <v>0.0001523392566014081</v>
+      </c>
+      <c r="CD9" t="n">
+        <v>0.000191763843758963</v>
+      </c>
+      <c r="CE9" t="n">
+        <v>0.0006970748654566705</v>
+      </c>
+      <c r="CF9" t="n">
+        <v>4.410655674291775e-05</v>
+      </c>
+      <c r="CG9" t="n">
+        <v>0.0001853388966992497</v>
+      </c>
+      <c r="CH9" t="n">
+        <v>0.0001254391827387735</v>
+      </c>
+      <c r="CI9" t="n">
+        <v>0.0002888176531996578</v>
+      </c>
+      <c r="CJ9" t="n">
+        <v>0.0001262616133317351</v>
+      </c>
+      <c r="CK9" t="n">
+        <v>9.778125240700319e-05</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>0.0001595535140950233</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>0.0004734520043712109</v>
+      </c>
+      <c r="CN9" t="n">
+        <v>0.001012002001516521</v>
+      </c>
+      <c r="CO9" t="n">
+        <v>0.0004660326812881976</v>
+      </c>
+      <c r="CP9" t="n">
+        <v>0.0004323011089581996</v>
+      </c>
+      <c r="CQ9" t="n">
+        <v>6.082182517275214e-05</v>
+      </c>
+      <c r="CR9" t="n">
+        <v>0.000443747965618968</v>
+      </c>
+      <c r="CS9" t="n">
+        <v>0.0001131522876676172</v>
+      </c>
+      <c r="CT9" t="n">
+        <v>0.0001607676385901868</v>
+      </c>
+      <c r="CU9" t="n">
+        <v>0.0002044582215603441</v>
+      </c>
+      <c r="CV9" t="n">
+        <v>9.008770575746894e-05</v>
+      </c>
+      <c r="CW9" t="n">
+        <v>0.0006435234099626541</v>
+      </c>
+      <c r="CX9" t="n">
+        <v>3.083498086198233e-05</v>
+      </c>
+      <c r="CY9" t="n">
+        <v>0.0001868826220743358</v>
+      </c>
+      <c r="CZ9" t="n">
+        <v>0.0001440374471712857</v>
+      </c>
+      <c r="DA9" t="n">
+        <v>0.0003083908231928945</v>
+      </c>
+      <c r="DB9" t="n">
+        <v>5.167709332454251e-06</v>
+      </c>
+      <c r="DC9" t="n">
+        <v>0.0002371484006289393</v>
+      </c>
+      <c r="DD9" t="n">
+        <v>0.000122489029308781</v>
+      </c>
+      <c r="DE9" t="n">
+        <v>0.0002883996930904686</v>
+      </c>
+      <c r="DF9" t="n">
+        <v>0.0002955097006633878</v>
+      </c>
+      <c r="DG9" t="n">
+        <v>0.0001606068108230829</v>
+      </c>
+      <c r="DH9" t="n">
+        <v>0.0003451934899203479</v>
+      </c>
+      <c r="DI9" t="n">
+        <v>0.0008428688743151724</v>
+      </c>
+      <c r="DJ9" t="n">
+        <v>4.4636195525527e-05</v>
+      </c>
+      <c r="DK9" t="n">
+        <v>0.0002532766666263342</v>
+      </c>
+      <c r="DL9" t="n">
+        <v>0.0001421871420461684</v>
+      </c>
+      <c r="DM9" t="n">
+        <v>6.096975994296372e-06</v>
+      </c>
+      <c r="DN9" t="n">
+        <v>0.0001498125493526459</v>
+      </c>
+      <c r="DO9" t="n">
+        <v>0.0004561659879982471</v>
+      </c>
+      <c r="DP9" t="n">
+        <v>0.0002028148737736046</v>
+      </c>
+      <c r="DQ9" t="n">
+        <v>4.031331263831817e-05</v>
+      </c>
+      <c r="DR9" t="n">
+        <v>0.000295978708891198</v>
+      </c>
+      <c r="DS9" t="n">
+        <v>0.0001932248414959759</v>
+      </c>
+      <c r="DT9" t="n">
+        <v>0.0002092736831400543</v>
+      </c>
+      <c r="DU9" t="n">
+        <v>0.0004088093701284379</v>
+      </c>
+      <c r="DV9" t="n">
+        <v>0.0002094848896376789</v>
+      </c>
+      <c r="DW9" t="n">
+        <v>0.0003283753467258066</v>
+      </c>
+      <c r="DX9" t="n">
+        <v>0.000225734751438722</v>
+      </c>
+      <c r="DY9" t="n">
+        <v>0.000264172675088048</v>
+      </c>
+      <c r="DZ9" t="n">
+        <v>0.0003729068266693503</v>
+      </c>
+      <c r="EA9" t="n">
+        <v>0.000160829906235449</v>
+      </c>
+      <c r="EB9" t="n">
+        <v>5.652225809171796e-06</v>
+      </c>
+      <c r="EC9" t="n">
+        <v>1.180831168312579e-05</v>
+      </c>
+      <c r="ED9" t="n">
+        <v>0.0003337943053338677</v>
+      </c>
+      <c r="EE9" t="n">
+        <v>0.0002039076789515093</v>
+      </c>
+      <c r="EF9" t="n">
+        <v>5.274900468066335e-05</v>
+      </c>
+      <c r="EG9" t="n">
+        <v>0.0001843181089498103</v>
+      </c>
+      <c r="EH9" t="n">
+        <v>0.0002748948172666132</v>
+      </c>
+      <c r="EI9" t="n">
+        <v>5.144511669641361e-05</v>
+      </c>
+      <c r="EJ9" t="n">
+        <v>2.073934228974395e-05</v>
+      </c>
+      <c r="EK9" t="n">
+        <v>0.0001453341101296246</v>
+      </c>
+      <c r="EL9" t="n">
+        <v>7.192573684733361e-05</v>
+      </c>
+      <c r="EM9" t="n">
+        <v>0.0002074259682558477</v>
+      </c>
+      <c r="EN9" t="n">
+        <v>8.972328214440495e-05</v>
+      </c>
+      <c r="EO9" t="n">
+        <v>0.0002673268609214574</v>
+      </c>
+      <c r="EP9" t="n">
+        <v>0.0003554380382411182</v>
+      </c>
+      <c r="EQ9" t="n">
+        <v>7.841813203413039e-05</v>
+      </c>
+      <c r="ER9" t="n">
+        <v>1.905590761452913e-05</v>
+      </c>
+      <c r="ES9" t="n">
+        <v>0.0002904667053371668</v>
+      </c>
+      <c r="ET9" t="n">
+        <v>0.0004469150444492698</v>
+      </c>
+      <c r="EU9" t="n">
+        <v>0.000159413815708831</v>
+      </c>
+      <c r="EV9" t="n">
+        <v>8.087469905149192e-05</v>
+      </c>
+      <c r="EW9" t="n">
+        <v>0.0001924666721606627</v>
+      </c>
+      <c r="EX9" t="n">
+        <v>0.0001774562697391957</v>
+      </c>
+      <c r="EY9" t="n">
+        <v>0.0007705118041485548</v>
+      </c>
+      <c r="EZ9" t="n">
+        <v>2.729791231104173e-05</v>
+      </c>
+      <c r="FA9" t="n">
+        <v>0.0002147095219697803</v>
+      </c>
+      <c r="FB9" t="n">
+        <v>6.767651939298958e-05</v>
+      </c>
+      <c r="FC9" t="n">
+        <v>0.0002509065670892596</v>
+      </c>
+      <c r="FD9" t="n">
+        <v>0.0001327997306361794</v>
+      </c>
+      <c r="FE9" t="n">
+        <v>0.0001574629714014009</v>
+      </c>
+      <c r="FF9" t="n">
+        <v>1.341141887678532e-05</v>
+      </c>
+      <c r="FG9" t="n">
+        <v>2.478839451214299e-05</v>
+      </c>
+      <c r="FH9" t="n">
+        <v>0.0004655745287891477</v>
+      </c>
+      <c r="FI9" t="n">
+        <v>0.0003246462438255548</v>
+      </c>
+      <c r="FJ9" t="n">
+        <v>0.0002434029884170741</v>
+      </c>
+      <c r="FK9" t="n">
+        <v>3.103189374087378e-05</v>
+      </c>
+      <c r="FL9" t="n">
+        <v>0.0004966693231835961</v>
+      </c>
+      <c r="FM9" t="n">
+        <v>0.0002275861334055662</v>
+      </c>
+      <c r="FN9" t="n">
+        <v>0.000287233357084915</v>
+      </c>
+      <c r="FO9" t="n">
+        <v>0.0004693145165219903</v>
+      </c>
+      <c r="FP9" t="n">
+        <v>0.000536164385266602</v>
+      </c>
+      <c r="FQ9" t="n">
+        <v>0.0008289487450383604</v>
+      </c>
+      <c r="FR9" t="n">
+        <v>0.0004653811920434237</v>
+      </c>
+      <c r="FS9" t="n">
+        <v>0.0005388662102632225</v>
+      </c>
+      <c r="FT9" t="n">
+        <v>0.0002682016929611564</v>
+      </c>
+      <c r="FU9" t="n">
+        <v>0.0005413158796727657</v>
+      </c>
+      <c r="FV9" t="n">
+        <v>0.0003424543829169124</v>
+      </c>
+      <c r="FW9" t="n">
+        <v>0.0001553257461637259</v>
+      </c>
+      <c r="FX9" t="n">
+        <v>0.000122478959383443</v>
+      </c>
+      <c r="FY9" t="n">
+        <v>0.000290041120024398</v>
+      </c>
+      <c r="FZ9" t="n">
+        <v>9.119231253862381e-05</v>
+      </c>
+      <c r="GA9" t="n">
+        <v>0.0003438754938542843</v>
+      </c>
+      <c r="GB9" t="n">
+        <v>6.463107274612412e-05</v>
+      </c>
+      <c r="GC9" t="n">
+        <v>3.572538844309747e-06</v>
+      </c>
+      <c r="GD9" t="n">
+        <v>0.0004895960446447134</v>
+      </c>
+      <c r="GE9" t="n">
+        <v>0.0003613299923017621</v>
+      </c>
+      <c r="GF9" t="n">
+        <v>0.0002733925357460976</v>
+      </c>
+      <c r="GG9" t="n">
+        <v>0.0001551188761368394</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>0</v>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER10" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES10" t="n">
+        <v>0</v>
+      </c>
+      <c r="ET10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>0.008006876334547997</v>
+      </c>
+      <c r="B11" t="n">
+        <v>0.01990574970841408</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.00539254117757082</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.0006889058277010918</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.001079136505723</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.03465268388390541</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.008150866255164146</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.03821375966072083</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.002933923155069351</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.007956402376294136</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.02234827354550362</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.006325609982013702</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.01363507658243179</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.00407213531434536</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.02387700974941254</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.0006596932653337717</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.0496368445456028</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.008851582184433937</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.002583668567240238</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.004043509252369404</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.001779689686372876</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.004370162263512611</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.006392064969986677</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.0001890988642117009</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.001981121953576803</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0.006089956499636173</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.002381081227213144</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.00208832835778594</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0.003197042969986796</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.003899392439052463</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0.01952137053012848</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0.01512269303202629</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0.003605587175115943</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0.01289375871419907</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0.005595390684902668</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0.005400441586971283</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0.002139980206266046</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0.007401748560369015</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0.008498349227011204</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0.003427713178098202</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0.01280594058334827</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0.01889974810183048</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0.006864965427666903</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0.005420112051069736</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0.003905531018972397</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0.002267573960125446</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0.05099945515394211</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0.004327575676143169</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0.005844161845743656</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0.01618479005992413</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>0.006645695772022009</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0.004082223400473595</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0.001854065572842956</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>0.01582477800548077</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>0.001583989826031029</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>0.04059449583292007</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>0.01018162071704865</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>0.003896710695698857</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>0.04113975539803505</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>0.009958509355783463</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>0.006155632436275482</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>0.004797149915248156</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>0.001697693020105362</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>0.003811085596680641</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>0.003253988455981016</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>0.01304663345217705</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>0.002035704907029867</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>0.004079055041074753</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>0.006370036862790585</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>0.0009386721067130566</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>0.01319273002445698</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>0.004165753722190857</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>0.0004590784665197134</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>0.02495099604129791</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>0.0008802094962447882</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>0.007294859737157822</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>0.00829159002751112</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>0.0109811844304204</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>0.006183596327900887</v>
+      </c>
+      <c r="CB11" t="n">
+        <v>0.004077326506376266</v>
+      </c>
+      <c r="CC11" t="n">
+        <v>0.001896071247756481</v>
+      </c>
+      <c r="CD11" t="n">
+        <v>0.000788174569606781</v>
+      </c>
+      <c r="CE11" t="n">
+        <v>0.008609620854258537</v>
+      </c>
+      <c r="CF11" t="n">
+        <v>0.006525703705847263</v>
+      </c>
+      <c r="CG11" t="n">
+        <v>0.001515828189440072</v>
+      </c>
+      <c r="CH11" t="n">
+        <v>0.004114607349038124</v>
+      </c>
+      <c r="CI11" t="n">
+        <v>0.009901503100991249</v>
+      </c>
+      <c r="CJ11" t="n">
+        <v>0.001747349160723388</v>
+      </c>
+      <c r="CK11" t="n">
+        <v>0.009907422587275505</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>0.002481870586052537</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>0.005675360094755888</v>
+      </c>
+      <c r="CN11" t="n">
+        <v>0.001320008770562708</v>
+      </c>
+      <c r="CO11" t="n">
+        <v>0.009806305170059204</v>
+      </c>
+      <c r="CP11" t="n">
+        <v>0.01736271008849144</v>
+      </c>
+      <c r="CQ11" t="n">
+        <v>0.03708578273653984</v>
+      </c>
+      <c r="CR11" t="n">
+        <v>0.0009910929948091507</v>
+      </c>
+      <c r="CS11" t="n">
+        <v>0.0007283217273652554</v>
+      </c>
+      <c r="CT11" t="n">
+        <v>0.008049620315432549</v>
+      </c>
+      <c r="CU11" t="n">
+        <v>0.002745056757703424</v>
+      </c>
+      <c r="CV11" t="n">
+        <v>0.001315964153036475</v>
+      </c>
+      <c r="CW11" t="n">
+        <v>0.006442067679017782</v>
+      </c>
+      <c r="CX11" t="n">
+        <v>0.004870614036917686</v>
+      </c>
+      <c r="CY11" t="n">
+        <v>0.0003942783805541694</v>
+      </c>
+      <c r="CZ11" t="n">
+        <v>0.003403187496587634</v>
+      </c>
+      <c r="DA11" t="n">
+        <v>0.009819344617426395</v>
+      </c>
+      <c r="DB11" t="n">
+        <v>1.180707477033138e-05</v>
+      </c>
+      <c r="DC11" t="n">
+        <v>0.00731393089517951</v>
+      </c>
+      <c r="DD11" t="n">
+        <v>0.001347284996882081</v>
+      </c>
+      <c r="DE11" t="n">
+        <v>0.01090648118406534</v>
+      </c>
+      <c r="DF11" t="n">
+        <v>0.02594455704092979</v>
+      </c>
+      <c r="DG11" t="n">
+        <v>0.007805121131241322</v>
+      </c>
+      <c r="DH11" t="n">
+        <v>0.01715913228690624</v>
+      </c>
+      <c r="DI11" t="n">
+        <v>0.02365105226635933</v>
+      </c>
+      <c r="DJ11" t="n">
+        <v>0.005966826342046261</v>
+      </c>
+      <c r="DK11" t="n">
+        <v>0.007225709035992622</v>
+      </c>
+      <c r="DL11" t="n">
+        <v>0.003942491021007299</v>
+      </c>
+      <c r="DM11" t="n">
+        <v>0.02045224979519844</v>
+      </c>
+      <c r="DN11" t="n">
+        <v>0.00572125893086195</v>
+      </c>
+      <c r="DO11" t="n">
+        <v>0.001561424694955349</v>
+      </c>
+      <c r="DP11" t="n">
+        <v>0.002326939953491092</v>
+      </c>
+      <c r="DQ11" t="n">
+        <v>0.004972299095243216</v>
+      </c>
+      <c r="DR11" t="n">
+        <v>0.001658513792790473</v>
+      </c>
+      <c r="DS11" t="n">
+        <v>0.003067117650061846</v>
+      </c>
+      <c r="DT11" t="n">
+        <v>0.001641450799070299</v>
+      </c>
+      <c r="DU11" t="n">
+        <v>0.002020981628447771</v>
+      </c>
+      <c r="DV11" t="n">
+        <v>0.002649649046361446</v>
+      </c>
+      <c r="DW11" t="n">
+        <v>0.0009965819772332907</v>
+      </c>
+      <c r="DX11" t="n">
+        <v>0.006439663469791412</v>
+      </c>
+      <c r="DY11" t="n">
+        <v>0.008860092610120773</v>
+      </c>
+      <c r="DZ11" t="n">
+        <v>0.0120308781042695</v>
+      </c>
+      <c r="EA11" t="n">
+        <v>0.002166638150811195</v>
+      </c>
+      <c r="EB11" t="n">
+        <v>0.004158302210271358</v>
+      </c>
+      <c r="EC11" t="n">
+        <v>0.004964908119291067</v>
+      </c>
+      <c r="ED11" t="n">
+        <v>0.001597214723005891</v>
+      </c>
+      <c r="EE11" t="n">
+        <v>0.0170184001326561</v>
+      </c>
+      <c r="EF11" t="n">
+        <v>0.002467116573825479</v>
+      </c>
+      <c r="EG11" t="n">
+        <v>0.001051807310432196</v>
+      </c>
+      <c r="EH11" t="n">
+        <v>0.002244768664240837</v>
+      </c>
+      <c r="EI11" t="n">
+        <v>0.006977292709052563</v>
+      </c>
+      <c r="EJ11" t="n">
+        <v>0.009476199746131897</v>
+      </c>
+      <c r="EK11" t="n">
+        <v>0.002126827836036682</v>
+      </c>
+      <c r="EL11" t="n">
+        <v>0.004434920381754637</v>
+      </c>
+      <c r="EM11" t="n">
+        <v>0.01266146637499332</v>
+      </c>
+      <c r="EN11" t="n">
+        <v>0.001335484208539128</v>
+      </c>
+      <c r="EO11" t="n">
+        <v>0.00229183561168611</v>
+      </c>
+      <c r="EP11" t="n">
+        <v>0.01161538250744343</v>
+      </c>
+      <c r="EQ11" t="n">
+        <v>0.001276969909667969</v>
+      </c>
+      <c r="ER11" t="n">
+        <v>0.002997023286297917</v>
+      </c>
+      <c r="ES11" t="n">
+        <v>0.007389340549707413</v>
+      </c>
+      <c r="ET11" t="n">
+        <v>0.01922289095818996</v>
+      </c>
+      <c r="EU11" t="n">
+        <v>0.0103755434975028</v>
+      </c>
+      <c r="EV11" t="n">
+        <v>0.01232296973466873</v>
+      </c>
+      <c r="EW11" t="n">
+        <v>0.01306341961026192</v>
+      </c>
+      <c r="EX11" t="n">
+        <v>0.0001807848457247019</v>
+      </c>
+      <c r="EY11" t="n">
+        <v>0.009168716147542</v>
+      </c>
+      <c r="EZ11" t="n">
+        <v>0.005767804104834795</v>
+      </c>
+      <c r="FA11" t="n">
+        <v>0.001145903719589114</v>
+      </c>
+      <c r="FB11" t="n">
+        <v>0.002277592197060585</v>
+      </c>
+      <c r="FC11" t="n">
+        <v>0.007776301354169846</v>
+      </c>
+      <c r="FD11" t="n">
+        <v>0.001055322587490082</v>
+      </c>
+      <c r="FE11" t="n">
+        <v>0.009119023568928242</v>
+      </c>
+      <c r="FF11" t="n">
+        <v>0.0002661769394762814</v>
+      </c>
+      <c r="FG11" t="n">
+        <v>0.003571425564587116</v>
+      </c>
+      <c r="FH11" t="n">
+        <v>0.01564574241638184</v>
+      </c>
+      <c r="FI11" t="n">
+        <v>0.001497183344326913</v>
+      </c>
+      <c r="FJ11" t="n">
+        <v>0.006538128480315208</v>
+      </c>
+      <c r="FK11" t="n">
+        <v>0.002329824026674032</v>
+      </c>
+      <c r="FL11" t="n">
+        <v>0.01168986968696117</v>
+      </c>
+      <c r="FM11" t="n">
+        <v>0.003455707337707281</v>
+      </c>
+      <c r="FN11" t="n">
+        <v>0.005649742670357227</v>
+      </c>
+      <c r="FO11" t="n">
+        <v>0.002227406948804855</v>
+      </c>
+      <c r="FP11" t="n">
+        <v>0.0006815723609179258</v>
+      </c>
+      <c r="FQ11" t="n">
+        <v>0.02922812476754189</v>
+      </c>
+      <c r="FR11" t="n">
+        <v>0.0507768988609314</v>
+      </c>
+      <c r="FS11" t="n">
+        <v>0.004892123863101006</v>
+      </c>
+      <c r="FT11" t="n">
+        <v>0.01187619939446449</v>
+      </c>
+      <c r="FU11" t="n">
+        <v>0.02408614009618759</v>
+      </c>
+      <c r="FV11" t="n">
+        <v>0.01158112846314907</v>
+      </c>
+      <c r="FW11" t="n">
+        <v>0.0009244857938028872</v>
+      </c>
+      <c r="FX11" t="n">
+        <v>0.03536368906497955</v>
+      </c>
+      <c r="FY11" t="n">
+        <v>0.009122783318161964</v>
+      </c>
+      <c r="FZ11" t="n">
+        <v>0.007316973526030779</v>
+      </c>
+      <c r="GA11" t="n">
+        <v>0.0002605309709906578</v>
+      </c>
+      <c r="GB11" t="n">
+        <v>0.005483148619532585</v>
+      </c>
+      <c r="GC11" t="n">
+        <v>0.00466469768434763</v>
+      </c>
+      <c r="GD11" t="n">
+        <v>0.002900579944252968</v>
+      </c>
+      <c r="GE11" t="n">
+        <v>0.0001490967115387321</v>
+      </c>
+      <c r="GF11" t="n">
+        <v>0.0156968217343092</v>
+      </c>
+      <c r="GG11" t="n">
+        <v>0.007800483610481024</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>3.074165420002828e-07</v>
+      </c>
+      <c r="B12" t="n">
+        <v>6.701253005303442e-05</v>
+      </c>
+      <c r="C12" t="n">
+        <v>2.429256710456684e-05</v>
+      </c>
+      <c r="D12" t="n">
+        <v>7.707356417085975e-06</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.95567754417425e-05</v>
+      </c>
+      <c r="F12" t="n">
+        <v>6.033369936631061e-05</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.041225232256693e-06</v>
+      </c>
+      <c r="H12" t="n">
+        <v>3.269231092417613e-05</v>
+      </c>
+      <c r="I12" t="n">
+        <v>5.682806659024209e-06</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2.947883331216872e-06</v>
+      </c>
+      <c r="K12" t="n">
+        <v>8.565112511860207e-05</v>
+      </c>
+      <c r="L12" t="n">
+        <v>3.641854345914908e-05</v>
+      </c>
+      <c r="M12" t="n">
+        <v>2.385793050052598e-05</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1.423023968527559e-05</v>
+      </c>
+      <c r="O12" t="n">
+        <v>6.114384450484067e-05</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.887429445763701e-06</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.346433211641852e-05</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6.979889349167934e-06</v>
+      </c>
+      <c r="S12" t="n">
+        <v>9.607233550923411e-07</v>
+      </c>
+      <c r="T12" t="n">
+        <v>8.679420716362074e-06</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.746007001202088e-06</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.007197170110885e-05</v>
+      </c>
+      <c r="W12" t="n">
+        <v>6.386580025719013e-06</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2.380933619861025e-05</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>5.19868308401783e-06</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.139991582022049e-05</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.323176320511266e-06</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.435632611901383e-06</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>6.008214768371545e-06</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>4.281071596778929e-06</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.42925709951669e-05</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.343856183666503e-05</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.53727232827805e-05</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>2.877662154787686e-06</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>3.234759424231015e-05</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>8.963068466982804e-06</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>3.667906185000902e-06</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1.707574483589269e-05</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>2.045497240033001e-06</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>1.164820787380449e-05</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>2.964975237773615e-06</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>8.26825726107927e-06</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>2.831254732882371e-07</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>1.551243440189864e-05</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>8.03677539806813e-06</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>1.029978011501953e-05</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>8.118545520119369e-05</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>6.593621947104111e-06</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>1.386935946356971e-05</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>2.927861169155221e-05</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>4.750889274873771e-05</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>1.342334599030437e-06</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>7.026053935987875e-06</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>9.234731805918273e-06</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>3.723709482983395e-07</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>2.141284130630083e-05</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>1.801923281163909e-05</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>5.875339184058248e-07</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>2.254260834888555e-05</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>1.942234462148917e-07</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>1.145082114817342e-05</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>9.027580745168962e-06</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>5.462269655254204e-06</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>4.227170848025708e-06</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>6.880100954731461e-06</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>4.886323040409479e-06</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>3.134422968287254e-06</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>3.60927060683025e-07</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>4.1911807784345e-06</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>5.00826627103379e-06</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>1.769942173268646e-06</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>5.729382792196702e-06</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>1.594060108800477e-06</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>4.159455784247257e-05</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>3.648727670224616e-06</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>1.331382554781158e-05</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>1.463762509956723e-05</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>3.577964889700525e-05</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>9.694030268292408e-06</v>
+      </c>
+      <c r="CB12" t="n">
+        <v>8.463940503133927e-06</v>
+      </c>
+      <c r="CC12" t="n">
+        <v>1.857786855907761e-06</v>
+      </c>
+      <c r="CD12" t="n">
+        <v>4.803821411769604e-07</v>
+      </c>
+      <c r="CE12" t="n">
+        <v>2.437574039504398e-05</v>
+      </c>
+      <c r="CF12" t="n">
+        <v>4.837932465306949e-06</v>
+      </c>
+      <c r="CG12" t="n">
+        <v>5.073679858469404e-06</v>
+      </c>
+      <c r="CH12" t="n">
+        <v>4.20492369812564e-07</v>
+      </c>
+      <c r="CI12" t="n">
+        <v>1.309293202211848e-05</v>
+      </c>
+      <c r="CJ12" t="n">
+        <v>2.606718680908671e-07</v>
+      </c>
+      <c r="CK12" t="n">
+        <v>6.117098109825747e-06</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>2.333557858946733e-06</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>4.755164809466805e-06</v>
+      </c>
+      <c r="CN12" t="n">
+        <v>1.646815871936269e-05</v>
+      </c>
+      <c r="CO12" t="n">
+        <v>1.602561678737402e-05</v>
+      </c>
+      <c r="CP12" t="n">
+        <v>2.299960942764301e-05</v>
+      </c>
+      <c r="CQ12" t="n">
+        <v>2.395009141764604e-05</v>
+      </c>
+      <c r="CR12" t="n">
+        <v>1.231142778124195e-05</v>
+      </c>
+      <c r="CS12" t="n">
+        <v>6.170057531562634e-06</v>
+      </c>
+      <c r="CT12" t="n">
+        <v>2.673733206393081e-06</v>
+      </c>
+      <c r="CU12" t="n">
+        <v>5.885304290131899e-06</v>
+      </c>
+      <c r="CV12" t="n">
+        <v>3.586422508305986e-06</v>
+      </c>
+      <c r="CW12" t="n">
+        <v>2.166457852581516e-05</v>
+      </c>
+      <c r="CX12" t="n">
+        <v>7.837095836293884e-06</v>
+      </c>
+      <c r="CY12" t="n">
+        <v>8.768720363150351e-06</v>
+      </c>
+      <c r="CZ12" t="n">
+        <v>1.494396883572335e-06</v>
+      </c>
+      <c r="DA12" t="n">
+        <v>1.536589661554899e-05</v>
+      </c>
+      <c r="DB12" t="n">
+        <v>2.130597522409516e-06</v>
+      </c>
+      <c r="DC12" t="n">
+        <v>3.970322723034769e-06</v>
+      </c>
+      <c r="DD12" t="n">
+        <v>1.694537559160381e-07</v>
+      </c>
+      <c r="DE12" t="n">
+        <v>1.925957349158125e-06</v>
+      </c>
+      <c r="DF12" t="n">
+        <v>1.50944761116989e-05</v>
+      </c>
+      <c r="DG12" t="n">
+        <v>6.676993507426232e-06</v>
+      </c>
+      <c r="DH12" t="n">
+        <v>6.450351975217927e-06</v>
+      </c>
+      <c r="DI12" t="n">
+        <v>4.333982815296622e-06</v>
+      </c>
+      <c r="DJ12" t="n">
+        <v>2.465932630002499e-05</v>
+      </c>
+      <c r="DK12" t="n">
+        <v>5.035110007156618e-06</v>
+      </c>
+      <c r="DL12" t="n">
+        <v>2.868089177354705e-05</v>
+      </c>
+      <c r="DM12" t="n">
+        <v>7.809741873643361e-06</v>
+      </c>
+      <c r="DN12" t="n">
+        <v>6.305757324298611e-06</v>
+      </c>
+      <c r="DO12" t="n">
+        <v>7.270863079611445e-06</v>
+      </c>
+      <c r="DP12" t="n">
+        <v>4.224270014674403e-06</v>
+      </c>
+      <c r="DQ12" t="n">
+        <v>4.080372946191346e-06</v>
+      </c>
+      <c r="DR12" t="n">
+        <v>1.370936047351279e-06</v>
+      </c>
+      <c r="DS12" t="n">
+        <v>9.306910214945674e-06</v>
+      </c>
+      <c r="DT12" t="n">
+        <v>6.453426976804622e-06</v>
+      </c>
+      <c r="DU12" t="n">
+        <v>1.338730908173602e-05</v>
+      </c>
+      <c r="DV12" t="n">
+        <v>3.888900209858548e-06</v>
+      </c>
+      <c r="DW12" t="n">
+        <v>1.163929482572712e-05</v>
+      </c>
+      <c r="DX12" t="n">
+        <v>1.356189841317246e-05</v>
+      </c>
+      <c r="DY12" t="n">
+        <v>1.138484731200151e-05</v>
+      </c>
+      <c r="DZ12" t="n">
+        <v>7.81657945481129e-07</v>
+      </c>
+      <c r="EA12" t="n">
+        <v>1.697421976132318e-05</v>
+      </c>
+      <c r="EB12" t="n">
+        <v>1.494805565016577e-05</v>
+      </c>
+      <c r="EC12" t="n">
+        <v>5.708491244149627e-06</v>
+      </c>
+      <c r="ED12" t="n">
+        <v>1.443642941012513e-05</v>
+      </c>
+      <c r="EE12" t="n">
+        <v>1.378651450067991e-05</v>
+      </c>
+      <c r="EF12" t="n">
+        <v>4.256005922798067e-06</v>
+      </c>
+      <c r="EG12" t="n">
+        <v>1.175962188426638e-05</v>
+      </c>
+      <c r="EH12" t="n">
+        <v>2.737189333856804e-06</v>
+      </c>
+      <c r="EI12" t="n">
+        <v>7.831827133486513e-07</v>
+      </c>
+      <c r="EJ12" t="n">
+        <v>7.341606760746799e-06</v>
+      </c>
+      <c r="EK12" t="n">
+        <v>4.318389983382076e-06</v>
+      </c>
+      <c r="EL12" t="n">
+        <v>3.897717306244886e-06</v>
+      </c>
+      <c r="EM12" t="n">
+        <v>5.659178441419499e-06</v>
+      </c>
+      <c r="EN12" t="n">
+        <v>3.872323759424035e-07</v>
+      </c>
+      <c r="EO12" t="n">
+        <v>7.955803994263988e-06</v>
+      </c>
+      <c r="EP12" t="n">
+        <v>8.717912351130508e-06</v>
+      </c>
+      <c r="EQ12" t="n">
+        <v>2.52282120527525e-06</v>
+      </c>
+      <c r="ER12" t="n">
+        <v>1.165401226899121e-05</v>
+      </c>
+      <c r="ES12" t="n">
+        <v>1.170693212770857e-05</v>
+      </c>
+      <c r="ET12" t="n">
+        <v>5.607948878605384e-07</v>
+      </c>
+      <c r="EU12" t="n">
+        <v>7.973227411639527e-07</v>
+      </c>
+      <c r="EV12" t="n">
+        <v>5.175739715923555e-06</v>
+      </c>
+      <c r="EW12" t="n">
+        <v>1.269725999009097e-05</v>
+      </c>
+      <c r="EX12" t="n">
+        <v>1.308267201238777e-07</v>
+      </c>
+      <c r="EY12" t="n">
+        <v>2.618878170324024e-05</v>
+      </c>
+      <c r="EZ12" t="n">
+        <v>5.782350399385905e-06</v>
+      </c>
+      <c r="FA12" t="n">
+        <v>7.359865321632242e-06</v>
+      </c>
+      <c r="FB12" t="n">
+        <v>1.32804416352883e-06</v>
+      </c>
+      <c r="FC12" t="n">
+        <v>1.554525624669623e-05</v>
+      </c>
+      <c r="FD12" t="n">
+        <v>1.072699888027273e-06</v>
+      </c>
+      <c r="FE12" t="n">
+        <v>5.994529601593968e-06</v>
+      </c>
+      <c r="FF12" t="n">
+        <v>1.915795564855216e-06</v>
+      </c>
+      <c r="FG12" t="n">
+        <v>2.697937588891364e-06</v>
+      </c>
+      <c r="FH12" t="n">
+        <v>1.736868580337614e-05</v>
+      </c>
+      <c r="FI12" t="n">
+        <v>6.64112394588301e-06</v>
+      </c>
+      <c r="FJ12" t="n">
+        <v>8.391791197936982e-06</v>
+      </c>
+      <c r="FK12" t="n">
+        <v>2.559713948357967e-06</v>
+      </c>
+      <c r="FL12" t="n">
+        <v>1.067052198777674e-05</v>
+      </c>
+      <c r="FM12" t="n">
+        <v>2.194973149016732e-06</v>
+      </c>
+      <c r="FN12" t="n">
+        <v>2.200277958763763e-05</v>
+      </c>
+      <c r="FO12" t="n">
+        <v>1.5581252228003e-05</v>
+      </c>
+      <c r="FP12" t="n">
+        <v>3.855076556646964e-06</v>
+      </c>
+      <c r="FQ12" t="n">
+        <v>1.628802783670835e-05</v>
+      </c>
+      <c r="FR12" t="n">
+        <v>1.682248148426879e-05</v>
+      </c>
+      <c r="FS12" t="n">
+        <v>1.513668848929228e-06</v>
+      </c>
+      <c r="FT12" t="n">
+        <v>9.882701306196395e-07</v>
+      </c>
+      <c r="FU12" t="n">
+        <v>1.159704515885096e-05</v>
+      </c>
+      <c r="FV12" t="n">
+        <v>1.528939174022526e-05</v>
+      </c>
+      <c r="FW12" t="n">
+        <v>1.546094608784188e-05</v>
+      </c>
+      <c r="FX12" t="n">
+        <v>1.672374128247611e-05</v>
+      </c>
+      <c r="FY12" t="n">
+        <v>6.837593900854699e-06</v>
+      </c>
+      <c r="FZ12" t="n">
+        <v>2.344072299820255e-06</v>
+      </c>
+      <c r="GA12" t="n">
+        <v>2.026801666943356e-05</v>
+      </c>
+      <c r="GB12" t="n">
+        <v>6.428622327803168e-07</v>
+      </c>
+      <c r="GC12" t="n">
+        <v>2.287203824380413e-05</v>
+      </c>
+      <c r="GD12" t="n">
+        <v>1.331642761215335e-05</v>
+      </c>
+      <c r="GE12" t="n">
+        <v>7.181743058026768e-06</v>
+      </c>
+      <c r="GF12" t="n">
+        <v>4.699178134615067e-06</v>
+      </c>
+      <c r="GG12" t="n">
+        <v>5.631813564832555e-06</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>0.0138594526797533</v>
+      </c>
+      <c r="B13" t="n">
+        <v>0.2014886438846588</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.07909369468688965</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.0002681082114577293</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.0005350853316485882</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.07447630167007446</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.01416070759296417</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.005689173936843872</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.08349337428808212</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.01303920336067677</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.2140951454639435</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.07895903289318085</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.04157803952693939</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.01210263557732105</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.02499697171151638</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.01815436966717243</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.02765398100018501</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.06655699759721756</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.002321450039744377</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.04593747481703758</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.05840082839131355</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.00202979682944715</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0.003715452970936894</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.0273488275706768</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.002901520347222686</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0.001989480806514621</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0.04037776961922646</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.03371293097734451</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0.03353464603424072</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.00871149729937315</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0.06925316900014877</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0.06533744186162949</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0.02426774427294731</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0.01661238074302673</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0.003466781228780746</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0.04974757879972458</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0.00135065009817481</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0.04674823954701424</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0.02814589254558086</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0.02038963139057159</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0.07753124088048935</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0.02644410729408264</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0.0004375679418444633</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0.003849063999950886</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0.00172579544596374</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0.02483098953962326</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0.1606118083000183</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0.01992252841591835</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0.03585038334131241</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0.007301939651370049</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0.03256534785032272</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>2.207758370786905e-05</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0.01798063516616821</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>0.04229332879185677</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>0.0368536114692688</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>0.01922118104994297</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>0.03769119083881378</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>0.02963830158114433</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>0.04979421943426132</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>0.04110165685415268</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>0.01475228648632765</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>0.0009099338203668594</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>0.01493593025952578</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>0.001166595611721277</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>0.04481054842472076</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>0.02580063790082932</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>0.04853731766343117</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>0.01322063151746988</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>0.004433023277670145</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>0.006985055282711983</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>0.02146378345787525</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>0.02442597597837448</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>0.003559029428288341</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>0.09057976305484772</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>0.01530543901026249</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>0.007147811818867922</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>0.001601226627826691</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>0.05111919716000557</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>0.004142869263887405</v>
+      </c>
+      <c r="CB13" t="n">
+        <v>0.006820493377745152</v>
+      </c>
+      <c r="CC13" t="n">
+        <v>0.04403504729270935</v>
+      </c>
+      <c r="CD13" t="n">
+        <v>0.003217346500605345</v>
+      </c>
+      <c r="CE13" t="n">
+        <v>0.06637629121541977</v>
+      </c>
+      <c r="CF13" t="n">
+        <v>0.04395469650626183</v>
+      </c>
+      <c r="CG13" t="n">
+        <v>0.01128632947802544</v>
+      </c>
+      <c r="CH13" t="n">
+        <v>0.001767314970493317</v>
+      </c>
+      <c r="CI13" t="n">
+        <v>0.008079937659204006</v>
+      </c>
+      <c r="CJ13" t="n">
+        <v>0.00286820693872869</v>
+      </c>
+      <c r="CK13" t="n">
+        <v>0.001413157675415277</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>0.01983702555298805</v>
+      </c>
+      <c r="CM13" t="n">
+        <v>0.0005991659127175808</v>
+      </c>
+      <c r="CN13" t="n">
+        <v>0.05529408901929855</v>
+      </c>
+      <c r="CO13" t="n">
+        <v>0.02968351915478706</v>
+      </c>
+      <c r="CP13" t="n">
+        <v>0.04532971978187561</v>
+      </c>
+      <c r="CQ13" t="n">
+        <v>0.05658679455518723</v>
+      </c>
+      <c r="CR13" t="n">
+        <v>0.05506854504346848</v>
+      </c>
+      <c r="CS13" t="n">
+        <v>0.003520323429256678</v>
+      </c>
+      <c r="CT13" t="n">
+        <v>0.004339233972132206</v>
+      </c>
+      <c r="CU13" t="n">
+        <v>0.005422721151262522</v>
+      </c>
+      <c r="CV13" t="n">
+        <v>0.007662517484277487</v>
+      </c>
+      <c r="CW13" t="n">
+        <v>0.06963285803794861</v>
+      </c>
+      <c r="CX13" t="n">
+        <v>0.04655224829912186</v>
+      </c>
+      <c r="CY13" t="n">
+        <v>0.01052348595112562</v>
+      </c>
+      <c r="CZ13" t="n">
+        <v>0.005648818798363209</v>
+      </c>
+      <c r="DA13" t="n">
+        <v>0.01683145016431808</v>
+      </c>
+      <c r="DB13" t="n">
+        <v>7.501663640141487e-05</v>
+      </c>
+      <c r="DC13" t="n">
+        <v>0.008113904856145382</v>
+      </c>
+      <c r="DD13" t="n">
+        <v>0.02950182929635048</v>
+      </c>
+      <c r="DE13" t="n">
+        <v>0.02236615121364594</v>
+      </c>
+      <c r="DF13" t="n">
+        <v>0.1071000248193741</v>
+      </c>
+      <c r="DG13" t="n">
+        <v>0.0705520436167717</v>
+      </c>
+      <c r="DH13" t="n">
+        <v>0.03702381998300552</v>
+      </c>
+      <c r="DI13" t="n">
+        <v>0.03037147596478462</v>
+      </c>
+      <c r="DJ13" t="n">
+        <v>0.02428424917161465</v>
+      </c>
+      <c r="DK13" t="n">
+        <v>0.002282176399603486</v>
+      </c>
+      <c r="DL13" t="n">
+        <v>0.01251260191202164</v>
+      </c>
+      <c r="DM13" t="n">
+        <v>0.04222122579813004</v>
+      </c>
+      <c r="DN13" t="n">
+        <v>0.01632010564208031</v>
+      </c>
+      <c r="DO13" t="n">
+        <v>0.008099695667624474</v>
+      </c>
+      <c r="DP13" t="n">
+        <v>0.04011612385511398</v>
+      </c>
+      <c r="DQ13" t="n">
+        <v>0.001539054326713085</v>
+      </c>
+      <c r="DR13" t="n">
+        <v>0.01807860285043716</v>
+      </c>
+      <c r="DS13" t="n">
+        <v>0.03461968898773193</v>
+      </c>
+      <c r="DT13" t="n">
+        <v>0.009328229352831841</v>
+      </c>
+      <c r="DU13" t="n">
+        <v>0.009027805179357529</v>
+      </c>
+      <c r="DV13" t="n">
+        <v>0.01799469627439976</v>
+      </c>
+      <c r="DW13" t="n">
+        <v>0.006303761154413223</v>
+      </c>
+      <c r="DX13" t="n">
+        <v>0.03085304424166679</v>
+      </c>
+      <c r="DY13" t="n">
+        <v>0.03209144622087479</v>
+      </c>
+      <c r="DZ13" t="n">
+        <v>0.008028427138924599</v>
+      </c>
+      <c r="EA13" t="n">
+        <v>0.0406082421541214</v>
+      </c>
+      <c r="EB13" t="n">
+        <v>0.03251810371875763</v>
+      </c>
+      <c r="EC13" t="n">
+        <v>0.005429547745734453</v>
+      </c>
+      <c r="ED13" t="n">
+        <v>0.01792843639850616</v>
+      </c>
+      <c r="EE13" t="n">
+        <v>0.02364045940339565</v>
+      </c>
+      <c r="EF13" t="n">
+        <v>0.003469561226665974</v>
+      </c>
+      <c r="EG13" t="n">
+        <v>0.07251377403736115</v>
+      </c>
+      <c r="EH13" t="n">
+        <v>0.02767040021717548</v>
+      </c>
+      <c r="EI13" t="n">
+        <v>0.003728773444890976</v>
+      </c>
+      <c r="EJ13" t="n">
+        <v>0.003590132808312774</v>
+      </c>
+      <c r="EK13" t="n">
+        <v>0.01594351977109909</v>
+      </c>
+      <c r="EL13" t="n">
+        <v>0.00641817320138216</v>
+      </c>
+      <c r="EM13" t="n">
+        <v>0.006289047189056873</v>
+      </c>
+      <c r="EN13" t="n">
+        <v>0.02623404003679752</v>
+      </c>
+      <c r="EO13" t="n">
+        <v>0.0199746061116457</v>
+      </c>
+      <c r="EP13" t="n">
+        <v>0.02468184940516949</v>
+      </c>
+      <c r="EQ13" t="n">
+        <v>0.01356371305882931</v>
+      </c>
+      <c r="ER13" t="n">
+        <v>0.0002859062515199184</v>
+      </c>
+      <c r="ES13" t="n">
+        <v>0.001298871356993914</v>
+      </c>
+      <c r="ET13" t="n">
+        <v>0.01048021484166384</v>
+      </c>
+      <c r="EU13" t="n">
+        <v>0.007032966241240501</v>
+      </c>
+      <c r="EV13" t="n">
+        <v>0.00457991287112236</v>
+      </c>
+      <c r="EW13" t="n">
+        <v>0.008866236545145512</v>
+      </c>
+      <c r="EX13" t="n">
+        <v>0.002411636523902416</v>
+      </c>
+      <c r="EY13" t="n">
+        <v>0.07064235955476761</v>
+      </c>
+      <c r="EZ13" t="n">
+        <v>0.04342649132013321</v>
+      </c>
+      <c r="FA13" t="n">
+        <v>0.01418593339622021</v>
+      </c>
+      <c r="FB13" t="n">
+        <v>0.004287136252969503</v>
+      </c>
+      <c r="FC13" t="n">
+        <v>0.01309425197541714</v>
+      </c>
+      <c r="FD13" t="n">
+        <v>0.001051270868629217</v>
+      </c>
+      <c r="FE13" t="n">
+        <v>0.002169866114854813</v>
+      </c>
+      <c r="FF13" t="n">
+        <v>0.02701463177800179</v>
+      </c>
+      <c r="FG13" t="n">
+        <v>0.009384467266499996</v>
+      </c>
+      <c r="FH13" t="n">
+        <v>0.05663962662220001</v>
+      </c>
+      <c r="FI13" t="n">
+        <v>0.01331167295575142</v>
+      </c>
+      <c r="FJ13" t="n">
+        <v>0.03659824654459953</v>
+      </c>
+      <c r="FK13" t="n">
+        <v>0.03335953503847122</v>
+      </c>
+      <c r="FL13" t="n">
+        <v>0.008480740711092949</v>
+      </c>
+      <c r="FM13" t="n">
+        <v>0.01090644672513008</v>
+      </c>
+      <c r="FN13" t="n">
+        <v>0.01610110327601433</v>
+      </c>
+      <c r="FO13" t="n">
+        <v>0.03906045854091644</v>
+      </c>
+      <c r="FP13" t="n">
+        <v>0.009365035220980644</v>
+      </c>
+      <c r="FQ13" t="n">
+        <v>0.07382631301879883</v>
+      </c>
+      <c r="FR13" t="n">
+        <v>0.09652338922023773</v>
+      </c>
+      <c r="FS13" t="n">
+        <v>0.04047407582402229</v>
+      </c>
+      <c r="FT13" t="n">
+        <v>0.006821898743510246</v>
+      </c>
+      <c r="FU13" t="n">
+        <v>0.02076570689678192</v>
+      </c>
+      <c r="FV13" t="n">
+        <v>0.007850689813494682</v>
+      </c>
+      <c r="FW13" t="n">
+        <v>0.03186572343111038</v>
+      </c>
+      <c r="FX13" t="n">
+        <v>0.0143289677798748</v>
+      </c>
+      <c r="FY13" t="n">
+        <v>0.06293994188308716</v>
+      </c>
+      <c r="FZ13" t="n">
+        <v>0.08043094724416733</v>
+      </c>
+      <c r="GA13" t="n">
+        <v>0.1105697900056839</v>
+      </c>
+      <c r="GB13" t="n">
+        <v>0.0007060831412672997</v>
+      </c>
+      <c r="GC13" t="n">
+        <v>0.01965549401938915</v>
+      </c>
+      <c r="GD13" t="n">
+        <v>0.009002561680972576</v>
+      </c>
+      <c r="GE13" t="n">
+        <v>0.01544036343693733</v>
+      </c>
+      <c r="GF13" t="n">
+        <v>0.0280404519289732</v>
+      </c>
+      <c r="GG13" t="n">
+        <v>0.02520805969834328</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>7.534665201092139e-05</v>
+      </c>
+      <c r="B14" t="n">
+        <v>0.0005576666444540024</v>
+      </c>
+      <c r="C14" t="n">
+        <v>7.226043817354366e-05</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.000266962219029665</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.0001723097084322944</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.0004957513883709908</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.0002880532410927117</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.0004255693638697267</v>
+      </c>
+      <c r="I14" t="n">
+        <v>8.628311479697004e-05</v>
+      </c>
+      <c r="J14" t="n">
+        <v>8.906482253223658e-05</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.0006556103471666574</v>
+      </c>
+      <c r="L14" t="n">
+        <v>4.42415512225125e-05</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.0004180268151685596</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.0003941507020499557</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.0006857254775241017</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.0002050140028586611</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.000204438591026701</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.0001953012397279963</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5.090924969408661e-05</v>
+      </c>
+      <c r="T14" t="n">
+        <v>4.118708602618426e-05</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.0001090407822630368</v>
+      </c>
+      <c r="V14" t="n">
+        <v>7.305834151338786e-05</v>
+      </c>
+      <c r="W14" t="n">
+        <v>9.064349433174357e-05</v>
+      </c>
+      <c r="X14" t="n">
+        <v>9.163391951005906e-05</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>6.288271833909675e-05</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0.0002684000646695495</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>4.241197893861681e-05</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.000125059625133872</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>8.013929618755355e-05</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>2.024113018705975e-05</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0.0001714860554784536</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0.0001393995771650225</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0.0002202152245445177</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>3.361756171216257e-06</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0.0004604438436217606</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>6.648371345363557e-05</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>9.869087080005556e-05</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>5.532935756491497e-05</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0.0001239554403582588</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>6.031141674611717e-05</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0.0001198409736389294</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>8.363959204871207e-05</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>3.791643030126579e-05</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0.0002839821972884238</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>5.179366780794226e-05</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0.000186721736099571</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0.0004530744336079806</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0.000103636208223179</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0.0001846690138336271</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0.0004541166126728058</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>0.0003557270392775536</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>1.596295987837948e-05</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0.0001033476728480309</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>5.128590419190004e-05</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>2.467464582878165e-05</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>0.0002494638611096889</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>4.750428342958912e-05</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>0.0002204653865192086</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>0.0002713287831284106</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>7.776821439620107e-05</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>0.0001042695803334936</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>0.0003898584109265357</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>2.578301791800186e-05</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>1.744247674650978e-05</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>0.0001566176651977003</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>1.257687290490139e-05</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>6.100985410739668e-05</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>0.0001192022536997683</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>1.082958624465391e-05</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>0.0003127656527794898</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>0.0001382174814352766</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>5.465006688609719e-05</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>7.937208283692598e-05</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>0.0001838900498114526</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>0.0001070218786480837</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>0.0001270293432753533</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>0.0001438798062736169</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>0.0001759260630933568</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>7.337889837799594e-05</v>
+      </c>
+      <c r="CB14" t="n">
+        <v>9.08596848603338e-05</v>
+      </c>
+      <c r="CC14" t="n">
+        <v>6.302618203335442e-06</v>
+      </c>
+      <c r="CD14" t="n">
+        <v>1.800347308744676e-05</v>
+      </c>
+      <c r="CE14" t="n">
+        <v>0.0001541579549666494</v>
+      </c>
+      <c r="CF14" t="n">
+        <v>6.107004992372822e-06</v>
+      </c>
+      <c r="CG14" t="n">
+        <v>9.130638500209898e-05</v>
+      </c>
+      <c r="CH14" t="n">
+        <v>7.570914021926001e-05</v>
+      </c>
+      <c r="CI14" t="n">
+        <v>0.0001640657865209505</v>
+      </c>
+      <c r="CJ14" t="n">
+        <v>7.068131526466459e-05</v>
+      </c>
+      <c r="CK14" t="n">
+        <v>1.986558891076129e-05</v>
+      </c>
+      <c r="CL14" t="n">
+        <v>5.918956594541669e-05</v>
+      </c>
+      <c r="CM14" t="n">
+        <v>4.937113408232108e-05</v>
+      </c>
+      <c r="CN14" t="n">
+        <v>0.0002526651951484382</v>
+      </c>
+      <c r="CO14" t="n">
+        <v>0.000278667634120211</v>
+      </c>
+      <c r="CP14" t="n">
+        <v>0.0003635098109953105</v>
+      </c>
+      <c r="CQ14" t="n">
+        <v>1.18881871458143e-05</v>
+      </c>
+      <c r="CR14" t="n">
+        <v>0.0001584499841555953</v>
+      </c>
+      <c r="CS14" t="n">
+        <v>6.294358900049701e-05</v>
+      </c>
+      <c r="CT14" t="n">
+        <v>0.0001448770490242168</v>
+      </c>
+      <c r="CU14" t="n">
+        <v>0.0001140822569141164</v>
+      </c>
+      <c r="CV14" t="n">
+        <v>4.393059134599753e-05</v>
+      </c>
+      <c r="CW14" t="n">
+        <v>0.0001403768837917596</v>
+      </c>
+      <c r="CX14" t="n">
+        <v>1.461784222556162e-07</v>
+      </c>
+      <c r="CY14" t="n">
+        <v>0.0001221128040924668</v>
+      </c>
+      <c r="CZ14" t="n">
+        <v>5.167398194316775e-05</v>
+      </c>
+      <c r="DA14" t="n">
+        <v>0.0001857460592873394</v>
+      </c>
+      <c r="DB14" t="n">
+        <v>1.354455434920965e-05</v>
+      </c>
+      <c r="DC14" t="n">
+        <v>6.652798219874967e-06</v>
+      </c>
+      <c r="DD14" t="n">
+        <v>2.273699283250608e-05</v>
+      </c>
+      <c r="DE14" t="n">
+        <v>6.404426676454023e-05</v>
+      </c>
+      <c r="DF14" t="n">
+        <v>6.493827095255256e-05</v>
+      </c>
+      <c r="DG14" t="n">
+        <v>0.0001894192537292838</v>
+      </c>
+      <c r="DH14" t="n">
+        <v>6.811545608798042e-05</v>
+      </c>
+      <c r="DI14" t="n">
+        <v>0.0004130098968744278</v>
+      </c>
+      <c r="DJ14" t="n">
+        <v>0.0001364727795589715</v>
+      </c>
+      <c r="DK14" t="n">
+        <v>7.568365253973752e-05</v>
+      </c>
+      <c r="DL14" t="n">
+        <v>0.0002460089162923396</v>
+      </c>
+      <c r="DM14" t="n">
+        <v>0.0001168984599644318</v>
+      </c>
+      <c r="DN14" t="n">
+        <v>7.64687720220536e-05</v>
+      </c>
+      <c r="DO14" t="n">
+        <v>0.0001253829395864159</v>
+      </c>
+      <c r="DP14" t="n">
+        <v>8.17667823866941e-05</v>
+      </c>
+      <c r="DQ14" t="n">
+        <v>9.521413448965177e-05</v>
+      </c>
+      <c r="DR14" t="n">
+        <v>1.343372059636749e-05</v>
+      </c>
+      <c r="DS14" t="n">
+        <v>9.4499964689021e-06</v>
+      </c>
+      <c r="DT14" t="n">
+        <v>0.0001213371797348373</v>
+      </c>
+      <c r="DU14" t="n">
+        <v>0.0002812955062836409</v>
+      </c>
+      <c r="DV14" t="n">
+        <v>6.935997225809842e-05</v>
+      </c>
+      <c r="DW14" t="n">
+        <v>6.528028461616486e-05</v>
+      </c>
+      <c r="DX14" t="n">
+        <v>8.306747622555122e-05</v>
+      </c>
+      <c r="DY14" t="n">
+        <v>1.157809492724482e-06</v>
+      </c>
+      <c r="DZ14" t="n">
+        <v>0.0002092532231472433</v>
+      </c>
+      <c r="EA14" t="n">
+        <v>0.0001907062687678263</v>
+      </c>
+      <c r="EB14" t="n">
+        <v>8.62476445036009e-05</v>
+      </c>
+      <c r="EC14" t="n">
+        <v>1.691512443358079e-05</v>
+      </c>
+      <c r="ED14" t="n">
+        <v>8.392377640120685e-05</v>
+      </c>
+      <c r="EE14" t="n">
+        <v>0.0002663755149114877</v>
+      </c>
+      <c r="EF14" t="n">
+        <v>7.179869044193765e-06</v>
+      </c>
+      <c r="EG14" t="n">
+        <v>3.84698978450615e-05</v>
+      </c>
+      <c r="EH14" t="n">
+        <v>6.069092341931537e-05</v>
+      </c>
+      <c r="EI14" t="n">
+        <v>1.854522997746244e-05</v>
+      </c>
+      <c r="EJ14" t="n">
+        <v>7.017249299678952e-05</v>
+      </c>
+      <c r="EK14" t="n">
+        <v>0.0002036009827861562</v>
+      </c>
+      <c r="EL14" t="n">
+        <v>7.315113907679915e-05</v>
+      </c>
+      <c r="EM14" t="n">
+        <v>7.017305961198872e-06</v>
+      </c>
+      <c r="EN14" t="n">
+        <v>3.504216874716803e-05</v>
+      </c>
+      <c r="EO14" t="n">
+        <v>4.79623704450205e-05</v>
+      </c>
+      <c r="EP14" t="n">
+        <v>8.23005975689739e-05</v>
+      </c>
+      <c r="EQ14" t="n">
+        <v>0.0001343863550573587</v>
+      </c>
+      <c r="ER14" t="n">
+        <v>0.0001055175744113512</v>
+      </c>
+      <c r="ES14" t="n">
+        <v>4.633619755622931e-05</v>
+      </c>
+      <c r="ET14" t="n">
+        <v>0.0001414238213328645</v>
+      </c>
+      <c r="EU14" t="n">
+        <v>7.387626828858629e-05</v>
+      </c>
+      <c r="EV14" t="n">
+        <v>1.91890612768475e-05</v>
+      </c>
+      <c r="EW14" t="n">
+        <v>0.0001125578710343689</v>
+      </c>
+      <c r="EX14" t="n">
+        <v>4.816601358470507e-05</v>
+      </c>
+      <c r="EY14" t="n">
+        <v>0.0002050547627732158</v>
+      </c>
+      <c r="EZ14" t="n">
+        <v>1.059525402524741e-06</v>
+      </c>
+      <c r="FA14" t="n">
+        <v>0.0001582198892720044</v>
+      </c>
+      <c r="FB14" t="n">
+        <v>4.600388274411671e-05</v>
+      </c>
+      <c r="FC14" t="n">
+        <v>0.0001600273681106046</v>
+      </c>
+      <c r="FD14" t="n">
+        <v>5.3911058785161e-05</v>
+      </c>
+      <c r="FE14" t="n">
+        <v>9.659115676186047e-07</v>
+      </c>
+      <c r="FF14" t="n">
+        <v>4.751405867864378e-06</v>
+      </c>
+      <c r="FG14" t="n">
+        <v>3.094939893344417e-05</v>
+      </c>
+      <c r="FH14" t="n">
+        <v>0.0002150612272089347</v>
+      </c>
+      <c r="FI14" t="n">
+        <v>0.0001922720111906528</v>
+      </c>
+      <c r="FJ14" t="n">
+        <v>8.973792137112468e-05</v>
+      </c>
+      <c r="FK14" t="n">
+        <v>0.0001440839696442708</v>
+      </c>
+      <c r="FL14" t="n">
+        <v>0.0001054538297466934</v>
+      </c>
+      <c r="FM14" t="n">
+        <v>0.0001108450887841173</v>
+      </c>
+      <c r="FN14" t="n">
+        <v>0.0001574684429215267</v>
+      </c>
+      <c r="FO14" t="n">
+        <v>0.0002202050527557731</v>
+      </c>
+      <c r="FP14" t="n">
+        <v>0.0001202642306452617</v>
+      </c>
+      <c r="FQ14" t="n">
+        <v>5.258404780761339e-05</v>
+      </c>
+      <c r="FR14" t="n">
+        <v>0.0003679635701701045</v>
+      </c>
+      <c r="FS14" t="n">
+        <v>0.0001386669464409351</v>
+      </c>
+      <c r="FT14" t="n">
+        <v>0.0002657397708389908</v>
+      </c>
+      <c r="FU14" t="n">
+        <v>5.152887024451047e-05</v>
+      </c>
+      <c r="FV14" t="n">
+        <v>2.819414658006281e-05</v>
+      </c>
+      <c r="FW14" t="n">
+        <v>0.0001601911790203303</v>
+      </c>
+      <c r="FX14" t="n">
+        <v>0.0001392734120599926</v>
+      </c>
+      <c r="FY14" t="n">
+        <v>2.178107752115466e-05</v>
+      </c>
+      <c r="FZ14" t="n">
+        <v>0.0002163868048228323</v>
+      </c>
+      <c r="GA14" t="n">
+        <v>0.0002044002321781591</v>
+      </c>
+      <c r="GB14" t="n">
+        <v>4.077413905179128e-05</v>
+      </c>
+      <c r="GC14" t="n">
+        <v>0.0002918321697507054</v>
+      </c>
+      <c r="GD14" t="n">
+        <v>0.0002643350453581661</v>
+      </c>
+      <c r="GE14" t="n">
+        <v>4.487401020014659e-05</v>
+      </c>
+      <c r="GF14" t="n">
+        <v>7.839269528631121e-05</v>
+      </c>
+      <c r="GG14" t="n">
+        <v>7.073197048157454e-05</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>0</v>
+      </c>
+      <c r="B15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER15" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES15" t="n">
+        <v>0</v>
+      </c>
+      <c r="ET15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>0</v>
+      </c>
+      <c r="B16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER16" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES16" t="n">
+        <v>0</v>
+      </c>
+      <c r="ET16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>7.554626790806651e-06</v>
+      </c>
+      <c r="B17" t="n">
+        <v>0.0002754486631602049</v>
+      </c>
+      <c r="C17" t="n">
+        <v>5.502663407241926e-05</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.0001462165964767337</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.0001399179018335417</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.0003619908238761127</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.0001706143957562745</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.0002385539701208472</v>
+      </c>
+      <c r="I17" t="n">
+        <v>7.239920523716137e-05</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2.291123564646114e-06</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.0003664773248601705</v>
+      </c>
+      <c r="L17" t="n">
+        <v>4.237943721818738e-05</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.0002207380603067577</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.0003150733537040651</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.0004802141047548503</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.0001079137000488117</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.000112999026896432</v>
+      </c>
+      <c r="R17" t="n">
+        <v>9.193950245389715e-05</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.754998422460631e-05</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.290384534513578e-05</v>
+      </c>
+      <c r="U17" t="n">
+        <v>6.247054261621088e-05</v>
+      </c>
+      <c r="V17" t="n">
+        <v>2.748030055954587e-05</v>
+      </c>
+      <c r="W17" t="n">
+        <v>3.262343670940027e-05</v>
+      </c>
+      <c r="X17" t="n">
+        <v>5.846372368978336e-05</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>5.582731319009326e-05</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0.0001744499459164217</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.412694630038459e-05</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>3.89712986361701e-05</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.308294667978771e-05</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>9.894029062706977e-06</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>7.503878441639245e-05</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0.0001311883970629424</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>7.280467980308458e-05</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.861169766925741e-05</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0.0002379000652581453</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>2.509978367015719e-05</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>2.176910129492171e-05</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>1.569565938552842e-05</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1.532400347059593e-06</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>2.400308403593954e-05</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>5.998814958729781e-05</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>5.790322393295355e-05</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>3.084833224420436e-05</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0.0001664635929046199</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>3.282420038885903e-06</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>5.925600999034941e-05</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>0.000348402390955016</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>1.377148146275431e-05</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>4.188874299870804e-05</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>0.0001759891893016174</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>0.0002788131241686642</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>1.867568789748475e-05</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>7.349184306804091e-05</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>3.768634633161128e-05</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>2.49532240559347e-06</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>8.923991117626429e-05</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>2.859854430425912e-05</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>0.0001468786940677091</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>9.086499630939215e-05</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>3.430104334256612e-05</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>5.001942554372363e-05</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>0.0001973840116988868</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>5.829126166645437e-05</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>8.061375410761684e-06</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>0.0001190886541735381</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>5.150572178536095e-06</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>8.577387052355334e-05</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>8.214979607146233e-05</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>2.8553748052218e-05</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>0.0001332530373474583</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>7.032876601442695e-05</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>6.742315599694848e-05</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>1.204423188028159e-05</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>0.0001661050628172234</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>2.74775975412922e-05</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>8.158424316206947e-05</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>4.699729470303282e-05</v>
+      </c>
+      <c r="BZ17" t="n">
+        <v>0.0001262191362911835</v>
+      </c>
+      <c r="CA17" t="n">
+        <v>2.806710290315095e-05</v>
+      </c>
+      <c r="CB17" t="n">
+        <v>7.043380901450291e-05</v>
+      </c>
+      <c r="CC17" t="n">
+        <v>4.12250665249303e-06</v>
+      </c>
+      <c r="CD17" t="n">
+        <v>2.085928645101376e-05</v>
+      </c>
+      <c r="CE17" t="n">
+        <v>6.928546645212919e-05</v>
+      </c>
+      <c r="CF17" t="n">
+        <v>4.46761578132282e-06</v>
+      </c>
+      <c r="CG17" t="n">
+        <v>6.235251203179359e-05</v>
+      </c>
+      <c r="CH17" t="n">
+        <v>4.705650280811824e-05</v>
+      </c>
+      <c r="CI17" t="n">
+        <v>0.0001075120308087207</v>
+      </c>
+      <c r="CJ17" t="n">
+        <v>4.456216265680268e-05</v>
+      </c>
+      <c r="CK17" t="n">
+        <v>1.008114850264974e-05</v>
+      </c>
+      <c r="CL17" t="n">
+        <v>2.736132228164934e-05</v>
+      </c>
+      <c r="CM17" t="n">
+        <v>4.308718416723423e-05</v>
+      </c>
+      <c r="CN17" t="n">
+        <v>0.000191124840057455</v>
+      </c>
+      <c r="CO17" t="n">
+        <v>0.0001006840320769697</v>
+      </c>
+      <c r="CP17" t="n">
+        <v>0.0001900326169561595</v>
+      </c>
+      <c r="CQ17" t="n">
+        <v>1.130203418142628e-05</v>
+      </c>
+      <c r="CR17" t="n">
+        <v>0.000100678123999387</v>
+      </c>
+      <c r="CS17" t="n">
+        <v>3.709238080773503e-05</v>
+      </c>
+      <c r="CT17" t="n">
+        <v>5.919846080360003e-05</v>
+      </c>
+      <c r="CU17" t="n">
+        <v>2.648674853844568e-05</v>
+      </c>
+      <c r="CV17" t="n">
+        <v>6.088473128329497e-06</v>
+      </c>
+      <c r="CW17" t="n">
+        <v>6.437175034079701e-05</v>
+      </c>
+      <c r="CX17" t="n">
+        <v>4.264413291821256e-06</v>
+      </c>
+      <c r="CY17" t="n">
+        <v>8.054561476456001e-05</v>
+      </c>
+      <c r="CZ17" t="n">
+        <v>4.039100531372242e-05</v>
+      </c>
+      <c r="DA17" t="n">
+        <v>0.0001276787661481649</v>
+      </c>
+      <c r="DB17" t="n">
+        <v>9.229500392393675e-06</v>
+      </c>
+      <c r="DC17" t="n">
+        <v>8.725637599127367e-07</v>
+      </c>
+      <c r="DD17" t="n">
+        <v>1.56251153384801e-05</v>
+      </c>
+      <c r="DE17" t="n">
+        <v>3.451423935985076e-06</v>
+      </c>
+      <c r="DF17" t="n">
+        <v>0.0001622140989638865</v>
+      </c>
+      <c r="DG17" t="n">
+        <v>8.418591460213065e-05</v>
+      </c>
+      <c r="DH17" t="n">
+        <v>1.822809099394362e-05</v>
+      </c>
+      <c r="DI17" t="n">
+        <v>0.0001754132972564548</v>
+      </c>
+      <c r="DJ17" t="n">
+        <v>0.0001100195731851272</v>
+      </c>
+      <c r="DK17" t="n">
+        <v>1.532948590465821e-05</v>
+      </c>
+      <c r="DL17" t="n">
+        <v>8.922476990846917e-05</v>
+      </c>
+      <c r="DM17" t="n">
+        <v>2.484361175447702e-05</v>
+      </c>
+      <c r="DN17" t="n">
+        <v>2.362649138376582e-05</v>
+      </c>
+      <c r="DO17" t="n">
+        <v>3.662891685962677e-06</v>
+      </c>
+      <c r="DP17" t="n">
+        <v>2.995444447151385e-05</v>
+      </c>
+      <c r="DQ17" t="n">
+        <v>3.965227006119676e-05</v>
+      </c>
+      <c r="DR17" t="n">
+        <v>1.270416760235094e-06</v>
+      </c>
+      <c r="DS17" t="n">
+        <v>2.244535153295146e-06</v>
+      </c>
+      <c r="DT17" t="n">
+        <v>7.32435510144569e-05</v>
+      </c>
+      <c r="DU17" t="n">
+        <v>0.0001454723824281245</v>
+      </c>
+      <c r="DV17" t="n">
+        <v>3.20238177664578e-05</v>
+      </c>
+      <c r="DW17" t="n">
+        <v>2.696034243854228e-05</v>
+      </c>
+      <c r="DX17" t="n">
+        <v>3.486333298496902e-05</v>
+      </c>
+      <c r="DY17" t="n">
+        <v>9.33820592763368e-06</v>
+      </c>
+      <c r="DZ17" t="n">
+        <v>0.0001294227840844542</v>
+      </c>
+      <c r="EA17" t="n">
+        <v>7.662392454221845e-05</v>
+      </c>
+      <c r="EB17" t="n">
+        <v>6.412101356545463e-05</v>
+      </c>
+      <c r="EC17" t="n">
+        <v>7.897247996879742e-06</v>
+      </c>
+      <c r="ED17" t="n">
+        <v>7.085907418513671e-05</v>
+      </c>
+      <c r="EE17" t="n">
+        <v>0.0001471258292440325</v>
+      </c>
+      <c r="EF17" t="n">
+        <v>2.351045986870304e-05</v>
+      </c>
+      <c r="EG17" t="n">
+        <v>2.378770295763388e-05</v>
+      </c>
+      <c r="EH17" t="n">
+        <v>4.419573815539479e-05</v>
+      </c>
+      <c r="EI17" t="n">
+        <v>1.505102409282699e-05</v>
+      </c>
+      <c r="EJ17" t="n">
+        <v>4.082029772689566e-05</v>
+      </c>
+      <c r="EK17" t="n">
+        <v>0.0001148322044173256</v>
+      </c>
+      <c r="EL17" t="n">
+        <v>5.689729732694104e-05</v>
+      </c>
+      <c r="EM17" t="n">
+        <v>2.565561590017751e-05</v>
+      </c>
+      <c r="EN17" t="n">
+        <v>6.913182915013749e-06</v>
+      </c>
+      <c r="EO17" t="n">
+        <v>1.477954356232658e-06</v>
+      </c>
+      <c r="EP17" t="n">
+        <v>8.180093573173508e-05</v>
+      </c>
+      <c r="EQ17" t="n">
+        <v>5.738369509344921e-05</v>
+      </c>
+      <c r="ER17" t="n">
+        <v>8.227476791944355e-05</v>
+      </c>
+      <c r="ES17" t="n">
+        <v>1.98731850105105e-05</v>
+      </c>
+      <c r="ET17" t="n">
+        <v>7.29490420781076e-05</v>
+      </c>
+      <c r="EU17" t="n">
+        <v>4.072104638908058e-05</v>
+      </c>
+      <c r="EV17" t="n">
+        <v>2.06279510166496e-05</v>
+      </c>
+      <c r="EW17" t="n">
+        <v>5.794341996079311e-05</v>
+      </c>
+      <c r="EX17" t="n">
+        <v>1.358070448986837e-06</v>
+      </c>
+      <c r="EY17" t="n">
+        <v>0.0001034770830301568</v>
+      </c>
+      <c r="EZ17" t="n">
+        <v>1.326303572568577e-05</v>
+      </c>
+      <c r="FA17" t="n">
+        <v>9.245890396414325e-05</v>
+      </c>
+      <c r="FB17" t="n">
+        <v>3.167131944792345e-05</v>
+      </c>
+      <c r="FC17" t="n">
+        <v>0.0001064886600943282</v>
+      </c>
+      <c r="FD17" t="n">
+        <v>3.522800034261309e-05</v>
+      </c>
+      <c r="FE17" t="n">
+        <v>2.761864834610606e-06</v>
+      </c>
+      <c r="FF17" t="n">
+        <v>1.399952793690318e-06</v>
+      </c>
+      <c r="FG17" t="n">
+        <v>7.806635039742105e-06</v>
+      </c>
+      <c r="FH17" t="n">
+        <v>0.0001109946315409616</v>
+      </c>
+      <c r="FI17" t="n">
+        <v>7.133724284358323e-05</v>
+      </c>
+      <c r="FJ17" t="n">
+        <v>3.42834900948219e-05</v>
+      </c>
+      <c r="FK17" t="n">
+        <v>9.000054706120864e-05</v>
+      </c>
+      <c r="FL17" t="n">
+        <v>8.756159513723105e-05</v>
+      </c>
+      <c r="FM17" t="n">
+        <v>8.29803102533333e-05</v>
+      </c>
+      <c r="FN17" t="n">
+        <v>4.91024911752902e-05</v>
+      </c>
+      <c r="FO17" t="n">
+        <v>0.0001022881624521688</v>
+      </c>
+      <c r="FP17" t="n">
+        <v>1.408884418196976e-05</v>
+      </c>
+      <c r="FQ17" t="n">
+        <v>4.471472493605688e-06</v>
+      </c>
+      <c r="FR17" t="n">
+        <v>0.0001684341405052692</v>
+      </c>
+      <c r="FS17" t="n">
+        <v>9.002887236420065e-05</v>
+      </c>
+      <c r="FT17" t="n">
+        <v>0.0002108096668962389</v>
+      </c>
+      <c r="FU17" t="n">
+        <v>4.371036629891023e-05</v>
+      </c>
+      <c r="FV17" t="n">
+        <v>3.06300753436517e-05</v>
+      </c>
+      <c r="FW17" t="n">
+        <v>0.0001288376952288672</v>
+      </c>
+      <c r="FX17" t="n">
+        <v>6.702392420265824e-05</v>
+      </c>
+      <c r="FY17" t="n">
+        <v>5.621531454380602e-05</v>
+      </c>
+      <c r="FZ17" t="n">
+        <v>9.877094998955727e-05</v>
+      </c>
+      <c r="GA17" t="n">
+        <v>9.334144851891324e-05</v>
+      </c>
+      <c r="GB17" t="n">
+        <v>1.525282459624577e-05</v>
+      </c>
+      <c r="GC17" t="n">
+        <v>0.000173146981978789</v>
+      </c>
+      <c r="GD17" t="n">
+        <v>0.000145695245009847</v>
+      </c>
+      <c r="GE17" t="n">
+        <v>8.853967301547527e-07</v>
+      </c>
+      <c r="GF17" t="n">
+        <v>8.099256956484169e-05</v>
+      </c>
+      <c r="GG17" t="n">
+        <v>6.466444756370038e-05</v>
       </c>
     </row>
   </sheetData>
